--- a/data/output/sim_gridrnd/REL2/group_480_20/results/REL2_G1_results_summary.xlsx
+++ b/data/output/sim_gridrnd/REL2/group_480_20/results/REL2_G1_results_summary.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CM23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,24 +436,24 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>mu</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sigma</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>jnd</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>pse</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>jnd</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>sigma</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>mu</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>n_trials</t>
@@ -466,1352 +466,1539 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>lat_entropy_100</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_120</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_140</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_160</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_180</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_200</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_40</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_60</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_80</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pse_40</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>jnd_40</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>pse_60</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>jnd_60</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>pse_80</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>jnd_80</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>pse_100</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>jnd_100</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pse_120</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>jnd_120</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>pse_140</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>jnd_140</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>pse_160</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>jnd_160</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>pse_180</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>jnd_180</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>pse_200</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>jnd_200</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_40</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_60</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_80</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_100</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_120</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_140</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_160</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_180</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_200</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_40</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_60</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_80</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_100</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_120</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_140</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_160</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_180</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_200</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_40</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_60</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_80</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_100</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_120</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_140</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_160</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_180</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_200</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_40</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_60</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_80</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_100</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_120</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_140</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_160</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_180</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_200</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_40</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_60</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_80</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_100</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_120</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_140</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_160</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_180</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_200</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_40</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_60</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_80</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_100</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_120</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_140</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_160</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_180</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_200</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>pse_est</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>jnd_est</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S03_G1_478_18_REL2</t>
+          <t>S01_G1_479_22_REL2</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>32.61675315048184</v>
       </c>
       <c r="D2" t="n">
-        <v>26.68643439584878</v>
+        <v>22</v>
       </c>
       <c r="E2" t="n">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F2" t="n">
         <v>200</v>
       </c>
       <c r="G2" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="H2" t="inlineStr">
+        <v>84.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>472.6380396029926</v>
-      </c>
-      <c r="J2" t="n">
-        <v>20.42708654571947</v>
-      </c>
-      <c r="K2" t="n">
-        <v>477.1783948871562</v>
-      </c>
-      <c r="L2" t="n">
-        <v>22.73848860080994</v>
-      </c>
-      <c r="M2" t="n">
-        <v>471.7492718152005</v>
-      </c>
-      <c r="N2" t="n">
-        <v>21.87164204189602</v>
-      </c>
-      <c r="O2" t="n">
-        <v>471.0479891252659</v>
-      </c>
-      <c r="P2" t="n">
-        <v>19.32032946832107</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>472.4283551788791</v>
-      </c>
       <c r="R2" t="n">
-        <v>20.7535740298553</v>
+        <v>470.68</v>
       </c>
       <c r="S2" t="n">
-        <v>472.3634281204336</v>
+        <v>32.73</v>
       </c>
       <c r="T2" t="n">
-        <v>21.10248707196239</v>
+        <v>474.25</v>
       </c>
       <c r="U2" t="n">
-        <v>471.0793039540815</v>
+        <v>28.8</v>
       </c>
       <c r="V2" t="n">
-        <v>21.38333346367916</v>
+        <v>477.97</v>
       </c>
       <c r="W2" t="n">
-        <v>471.4918412153972</v>
+        <v>28.63</v>
       </c>
       <c r="X2" t="n">
-        <v>20.90135296648325</v>
+        <v>476.71</v>
       </c>
       <c r="Y2" t="n">
-        <v>472.9254666877616</v>
+        <v>27.92</v>
       </c>
       <c r="Z2" t="n">
-        <v>21.45223386250381</v>
+        <v>472.65</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>26.15</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>474.87</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>23.51</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>477.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>25.67</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>476.18</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>25.18</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>475.72</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>23.79</v>
       </c>
       <c r="AJ2" t="n">
-        <v>485.4</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>483.6833333333333</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>482.4875</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>481.07</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>481</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>481.1214285714286</v>
+        <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>480.24375</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>479.9888888888889</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>479.99</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>71.51776003203679</v>
+        <v>482.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>60.89649460810988</v>
+        <v>481.4166666666667</v>
       </c>
       <c r="AU2" t="n">
-        <v>54.64727663616917</v>
+        <v>482.025</v>
       </c>
       <c r="AV2" t="n">
-        <v>50.65456642791447</v>
+        <v>481.63</v>
       </c>
       <c r="AW2" t="n">
-        <v>47.21105096620211</v>
+        <v>481.875</v>
       </c>
       <c r="AX2" t="n">
-        <v>44.59619904641823</v>
+        <v>481.9357142857143</v>
       </c>
       <c r="AY2" t="n">
-        <v>43.09578675389857</v>
+        <v>483.36875</v>
       </c>
       <c r="AZ2" t="n">
-        <v>41.5947364310129</v>
+        <v>483.5166666666667</v>
       </c>
       <c r="BA2" t="n">
-        <v>40.30235601053616</v>
+        <v>483.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>335</v>
+        <v>74.86527900168409</v>
       </c>
       <c r="BC2" t="n">
-        <v>335</v>
+        <v>65.18928635562408</v>
       </c>
       <c r="BD2" t="n">
-        <v>335</v>
+        <v>58.67707708296316</v>
       </c>
       <c r="BE2" t="n">
-        <v>335</v>
+        <v>54.48846758718766</v>
       </c>
       <c r="BF2" t="n">
-        <v>335</v>
+        <v>50.90310444036461</v>
       </c>
       <c r="BG2" t="n">
-        <v>335</v>
+        <v>48.00509061016129</v>
       </c>
       <c r="BH2" t="n">
-        <v>335</v>
+        <v>46.14875700858583</v>
       </c>
       <c r="BI2" t="n">
-        <v>335</v>
+        <v>45.50512486400723</v>
       </c>
       <c r="BJ2" t="n">
-        <v>335</v>
+        <v>44.20407221060069</v>
       </c>
       <c r="BK2" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BL2" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BM2" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BN2" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BO2" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BP2" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BQ2" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BR2" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BS2" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.8888888888888888</v>
+        <v>669</v>
       </c>
       <c r="BU2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="CF2" t="n">
         <v>0.5789473684210527</v>
       </c>
-      <c r="BV2" t="n">
-        <v>0.4827586206896552</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>0.5128205128205128</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>0.4897959183673469</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0.4430379746835443</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>0.4698795180722892</v>
+      <c r="CG2" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>0.6037735849056604</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>0.5892857142857143</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>0.5303030303030303</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>475.72</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>23.79</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S04_G1_478_22_REL2</t>
+          <t>S02_G1_481_20_REL2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>29.65159377316531</v>
       </c>
       <c r="D3" t="n">
-        <v>32.61675315048184</v>
+        <v>20</v>
       </c>
       <c r="E3" t="n">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="F3" t="n">
         <v>200</v>
       </c>
       <c r="G3" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="H3" t="inlineStr">
+        <v>83.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>476.9787399238213</v>
-      </c>
-      <c r="J3" t="n">
-        <v>35.26271283169524</v>
-      </c>
-      <c r="K3" t="n">
-        <v>479.1594530918912</v>
-      </c>
-      <c r="L3" t="n">
-        <v>31.18595037900932</v>
-      </c>
-      <c r="M3" t="n">
-        <v>472.620529216444</v>
-      </c>
-      <c r="N3" t="n">
-        <v>27.725668992504</v>
-      </c>
-      <c r="O3" t="n">
-        <v>474.2105669057979</v>
-      </c>
-      <c r="P3" t="n">
-        <v>27.09754866555214</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>471.9174170770031</v>
-      </c>
       <c r="R3" t="n">
-        <v>26.61516862555269</v>
+        <v>467.86</v>
       </c>
       <c r="S3" t="n">
-        <v>471.6163104659953</v>
+        <v>22.14</v>
       </c>
       <c r="T3" t="n">
-        <v>25.53637592681759</v>
+        <v>476.31</v>
       </c>
       <c r="U3" t="n">
-        <v>470.8227361901227</v>
+        <v>23.99</v>
       </c>
       <c r="V3" t="n">
-        <v>23.78343244042845</v>
+        <v>473.24</v>
       </c>
       <c r="W3" t="n">
-        <v>470.7163284830168</v>
+        <v>21.12</v>
       </c>
       <c r="X3" t="n">
-        <v>23.14651814948865</v>
+        <v>481.22</v>
       </c>
       <c r="Y3" t="n">
-        <v>471.4186671644678</v>
+        <v>23.19</v>
       </c>
       <c r="Z3" t="n">
-        <v>24.75546165355148</v>
+        <v>482.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>21.01</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>483.43</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>22.17</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>481.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>22.11</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>482.88</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>21.62</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>482.8</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>20.71</v>
       </c>
       <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>491.25</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>487.4333333333333</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>485.4625</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>484.17</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>483.6333333333333</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>484.0071428571429</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>484.18125</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>484.5444444444444</v>
+      </c>
+      <c r="BA3" t="n">
         <v>484.7</v>
       </c>
-      <c r="AK3" t="n">
-        <v>483.4833333333333</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>483.1</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>482</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>481.95</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>481.1285714285714</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>480.73125</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>480.1722222222222</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>479.775</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>78.63021047917906</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>68.19029541576198</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>61.06381907480075</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>56.19768678513378</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>52.29656617153113</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>49.6802408058839</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>47.38310905203984</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>45.56958422207558</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>44.23589464450787</v>
-      </c>
       <c r="BB3" t="n">
-        <v>343</v>
+        <v>70.01526619245263</v>
       </c>
       <c r="BC3" t="n">
-        <v>343</v>
+        <v>60.4798497205658</v>
       </c>
       <c r="BD3" t="n">
-        <v>343</v>
+        <v>54.65778621340238</v>
       </c>
       <c r="BE3" t="n">
-        <v>343</v>
+        <v>50.81280448863259</v>
       </c>
       <c r="BF3" t="n">
-        <v>343</v>
+        <v>47.74549426094804</v>
       </c>
       <c r="BG3" t="n">
-        <v>343</v>
+        <v>45.06130687797481</v>
       </c>
       <c r="BH3" t="n">
-        <v>343</v>
+        <v>42.90117595634763</v>
       </c>
       <c r="BI3" t="n">
-        <v>343</v>
+        <v>41.41850394613261</v>
       </c>
       <c r="BJ3" t="n">
-        <v>343</v>
+        <v>39.85122331873891</v>
       </c>
       <c r="BK3" t="n">
-        <v>669</v>
+        <v>333</v>
       </c>
       <c r="BL3" t="n">
-        <v>669</v>
+        <v>333</v>
       </c>
       <c r="BM3" t="n">
-        <v>669</v>
+        <v>333</v>
       </c>
       <c r="BN3" t="n">
-        <v>669</v>
+        <v>333</v>
       </c>
       <c r="BO3" t="n">
-        <v>669</v>
+        <v>333</v>
       </c>
       <c r="BP3" t="n">
-        <v>669</v>
+        <v>333</v>
       </c>
       <c r="BQ3" t="n">
-        <v>669</v>
+        <v>333</v>
       </c>
       <c r="BR3" t="n">
-        <v>669</v>
+        <v>333</v>
       </c>
       <c r="BS3" t="n">
-        <v>669</v>
+        <v>333</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.5555555555555556</v>
+        <v>669</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.8181818181818182</v>
+        <v>669</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.75</v>
+        <v>669</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.92</v>
+        <v>669</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.8125</v>
+        <v>669</v>
       </c>
       <c r="BY3" t="n">
-        <v>1</v>
+        <v>669</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.85</v>
+        <v>669</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.72</v>
+        <v>669</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.7636363636363637</v>
+        <v>669</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>0.5357142857142857</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>0.5657894736842105</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>0.5581395348837209</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>482.8</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>20.71</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S02_G1_481_20_REL2</t>
+          <t>S03_G1_478_18_REL2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>26.68643439584878</v>
       </c>
       <c r="D4" t="n">
-        <v>29.65159377316531</v>
+        <v>18</v>
       </c>
       <c r="E4" t="n">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="F4" t="n">
         <v>200</v>
       </c>
       <c r="G4" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="H4" t="inlineStr">
+        <v>83.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>467.8578491460752</v>
-      </c>
-      <c r="J4" t="n">
-        <v>22.13660563805604</v>
-      </c>
-      <c r="K4" t="n">
-        <v>476.3128364854466</v>
-      </c>
-      <c r="L4" t="n">
-        <v>23.99253878671666</v>
-      </c>
-      <c r="M4" t="n">
-        <v>473.2358423194078</v>
-      </c>
-      <c r="N4" t="n">
-        <v>21.12372611421545</v>
-      </c>
-      <c r="O4" t="n">
-        <v>481.2166367543159</v>
-      </c>
-      <c r="P4" t="n">
-        <v>23.1929220517506</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>482.601093101943</v>
-      </c>
       <c r="R4" t="n">
-        <v>21.00971142363265</v>
+        <v>472.64</v>
       </c>
       <c r="S4" t="n">
-        <v>483.4270667323033</v>
+        <v>20.43</v>
       </c>
       <c r="T4" t="n">
-        <v>22.16858764209796</v>
+        <v>477.18</v>
       </c>
       <c r="U4" t="n">
-        <v>481.3000751838388</v>
+        <v>22.74</v>
       </c>
       <c r="V4" t="n">
-        <v>22.11426122510577</v>
+        <v>471.75</v>
       </c>
       <c r="W4" t="n">
-        <v>482.8798220042201</v>
+        <v>21.87</v>
       </c>
       <c r="X4" t="n">
-        <v>21.61986387519224</v>
+        <v>471.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>482.7951782720488</v>
+        <v>19.32</v>
       </c>
       <c r="Z4" t="n">
-        <v>20.70573255696381</v>
+        <v>472.43</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>20.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>472.36</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>21.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>471.08</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>21.38</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>471.49</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>472.93</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>21.45</v>
       </c>
       <c r="AJ4" t="n">
-        <v>491.25</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>487.4333333333333</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>485.4625</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>484.17</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>483.6333333333333</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>484.0071428571429</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>484.18125</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>484.5444444444444</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>484.7</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>70.01526619245263</v>
+        <v>485.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>60.4798497205658</v>
+        <v>483.6833333333333</v>
       </c>
       <c r="AU4" t="n">
-        <v>54.65778621340238</v>
+        <v>482.4875</v>
       </c>
       <c r="AV4" t="n">
-        <v>50.81280448863259</v>
+        <v>481.07</v>
       </c>
       <c r="AW4" t="n">
-        <v>47.74549426094804</v>
+        <v>481</v>
       </c>
       <c r="AX4" t="n">
-        <v>45.06130687797481</v>
+        <v>481.1214285714286</v>
       </c>
       <c r="AY4" t="n">
-        <v>42.90117595634763</v>
+        <v>480.24375</v>
       </c>
       <c r="AZ4" t="n">
-        <v>41.41850394613261</v>
+        <v>479.9888888888889</v>
       </c>
       <c r="BA4" t="n">
-        <v>39.85122331873891</v>
+        <v>479.99</v>
       </c>
       <c r="BB4" t="n">
-        <v>333</v>
+        <v>71.51776003203679</v>
       </c>
       <c r="BC4" t="n">
-        <v>333</v>
+        <v>60.89649460810988</v>
       </c>
       <c r="BD4" t="n">
-        <v>333</v>
+        <v>54.64727663616917</v>
       </c>
       <c r="BE4" t="n">
-        <v>333</v>
+        <v>50.65456642791447</v>
       </c>
       <c r="BF4" t="n">
-        <v>333</v>
+        <v>47.21105096620211</v>
       </c>
       <c r="BG4" t="n">
-        <v>333</v>
+        <v>44.59619904641823</v>
       </c>
       <c r="BH4" t="n">
-        <v>333</v>
+        <v>43.09578675389857</v>
       </c>
       <c r="BI4" t="n">
-        <v>333</v>
+        <v>41.5947364310129</v>
       </c>
       <c r="BJ4" t="n">
-        <v>333</v>
+        <v>40.30235601053616</v>
       </c>
       <c r="BK4" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BL4" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BM4" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BN4" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BO4" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BP4" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BQ4" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BR4" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BS4" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.5833333333333334</v>
+        <v>669</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.5357142857142857</v>
+        <v>669</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.5454545454545454</v>
+        <v>669</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.5657894736842105</v>
+        <v>669</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.5581395348837209</v>
+        <v>669</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0.5789473684210527</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0.4827586206896552</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0.5128205128205128</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>0.4897959183673469</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>0.4430379746835443</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0.4698795180722892</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>472.93</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>21.45</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S01_G1_479_22_REL2</t>
+          <t>S04_G1_478_22_REL2</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C5" t="n">
+        <v>32.61675315048184</v>
+      </c>
+      <c r="D5" t="n">
         <v>22</v>
       </c>
-      <c r="D5" t="n">
-        <v>32.61675315048184</v>
-      </c>
       <c r="E5" t="n">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F5" t="n">
         <v>200</v>
       </c>
       <c r="G5" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="H5" t="inlineStr">
+        <v>83.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>470.675729944736</v>
-      </c>
-      <c r="J5" t="n">
-        <v>32.73203107282517</v>
-      </c>
-      <c r="K5" t="n">
-        <v>474.2541550034323</v>
-      </c>
-      <c r="L5" t="n">
-        <v>28.79982481564072</v>
-      </c>
-      <c r="M5" t="n">
-        <v>477.9715177280916</v>
-      </c>
-      <c r="N5" t="n">
-        <v>28.62886250767026</v>
-      </c>
-      <c r="O5" t="n">
-        <v>476.7135565110885</v>
-      </c>
-      <c r="P5" t="n">
-        <v>27.9171357388251</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>472.6531554475807</v>
-      </c>
       <c r="R5" t="n">
-        <v>26.14858295800089</v>
+        <v>476.98</v>
       </c>
       <c r="S5" t="n">
-        <v>474.8661415602821</v>
+        <v>35.26</v>
       </c>
       <c r="T5" t="n">
-        <v>23.51266226979773</v>
+        <v>479.16</v>
       </c>
       <c r="U5" t="n">
-        <v>477.8091299655662</v>
+        <v>31.19</v>
       </c>
       <c r="V5" t="n">
-        <v>25.66747422073072</v>
+        <v>472.62</v>
       </c>
       <c r="W5" t="n">
-        <v>476.1751514592843</v>
+        <v>27.73</v>
       </c>
       <c r="X5" t="n">
-        <v>25.1831219763449</v>
+        <v>474.21</v>
       </c>
       <c r="Y5" t="n">
-        <v>475.7236898912332</v>
+        <v>27.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>23.79239291553515</v>
+        <v>471.92</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>26.62</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>471.62</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>25.54</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>470.82</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>23.78</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>470.72</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>23.15</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>471.42</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>24.76</v>
       </c>
       <c r="AJ5" t="n">
-        <v>482.8</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>481.4166666666667</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>482.025</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>481.63</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>481.875</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>481.9357142857143</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>483.36875</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>483.5166666666667</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>483.5</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>74.86527900168409</v>
+        <v>484.7</v>
       </c>
       <c r="AT5" t="n">
-        <v>65.18928635562408</v>
+        <v>483.4833333333333</v>
       </c>
       <c r="AU5" t="n">
-        <v>58.67707708296316</v>
+        <v>483.1</v>
       </c>
       <c r="AV5" t="n">
-        <v>54.48846758718766</v>
+        <v>482</v>
       </c>
       <c r="AW5" t="n">
-        <v>50.90310444036461</v>
+        <v>481.95</v>
       </c>
       <c r="AX5" t="n">
-        <v>48.00509061016129</v>
+        <v>481.1285714285714</v>
       </c>
       <c r="AY5" t="n">
-        <v>46.14875700858583</v>
+        <v>480.73125</v>
       </c>
       <c r="AZ5" t="n">
-        <v>45.50512486400723</v>
+        <v>480.1722222222222</v>
       </c>
       <c r="BA5" t="n">
-        <v>44.20407221060069</v>
+        <v>479.775</v>
       </c>
       <c r="BB5" t="n">
-        <v>342</v>
+        <v>78.63021047917906</v>
       </c>
       <c r="BC5" t="n">
-        <v>342</v>
+        <v>68.19029541576198</v>
       </c>
       <c r="BD5" t="n">
-        <v>342</v>
+        <v>61.06381907480075</v>
       </c>
       <c r="BE5" t="n">
-        <v>342</v>
+        <v>56.19768678513378</v>
       </c>
       <c r="BF5" t="n">
-        <v>342</v>
+        <v>52.29656617153113</v>
       </c>
       <c r="BG5" t="n">
-        <v>342</v>
+        <v>49.6802408058839</v>
       </c>
       <c r="BH5" t="n">
-        <v>342</v>
+        <v>47.38310905203984</v>
       </c>
       <c r="BI5" t="n">
-        <v>342</v>
+        <v>45.56958422207558</v>
       </c>
       <c r="BJ5" t="n">
-        <v>342</v>
+        <v>44.23589464450787</v>
       </c>
       <c r="BK5" t="n">
-        <v>669</v>
+        <v>343</v>
       </c>
       <c r="BL5" t="n">
-        <v>669</v>
+        <v>343</v>
       </c>
       <c r="BM5" t="n">
-        <v>669</v>
+        <v>343</v>
       </c>
       <c r="BN5" t="n">
-        <v>669</v>
+        <v>343</v>
       </c>
       <c r="BO5" t="n">
-        <v>669</v>
+        <v>343</v>
       </c>
       <c r="BP5" t="n">
-        <v>669</v>
+        <v>343</v>
       </c>
       <c r="BQ5" t="n">
-        <v>669</v>
+        <v>343</v>
       </c>
       <c r="BR5" t="n">
-        <v>669</v>
+        <v>343</v>
       </c>
       <c r="BS5" t="n">
-        <v>669</v>
+        <v>343</v>
       </c>
       <c r="BT5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="CH5" t="n">
         <v>1</v>
       </c>
-      <c r="BU5" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>0.5789473684210527</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>0.5416666666666666</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>0.6037735849056604</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>0.5892857142857143</v>
-      </c>
-      <c r="CB5" t="n">
-        <v>0.5303030303030303</v>
+      <c r="CI5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0.7636363636363637</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>471.42</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>24.76</v>
       </c>
     </row>
     <row r="6">
@@ -1824,10 +2011,10 @@
         <v>481</v>
       </c>
       <c r="C6" t="n">
+        <v>31.13417346182357</v>
+      </c>
+      <c r="D6" t="n">
         <v>21</v>
-      </c>
-      <c r="D6" t="n">
-        <v>31.13417346182357</v>
       </c>
       <c r="E6" t="n">
         <v>481</v>
@@ -1836,228 +2023,261 @@
         <v>200</v>
       </c>
       <c r="G6" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="H6" t="inlineStr">
+        <v>82.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>480.4279411931017</v>
-      </c>
-      <c r="J6" t="n">
-        <v>28.61695707278323</v>
-      </c>
-      <c r="K6" t="n">
-        <v>479.4163126944317</v>
-      </c>
-      <c r="L6" t="n">
-        <v>30.21690766598677</v>
-      </c>
-      <c r="M6" t="n">
-        <v>482.7334836613507</v>
-      </c>
-      <c r="N6" t="n">
-        <v>24.30689311744045</v>
-      </c>
-      <c r="O6" t="n">
-        <v>480.8725133989641</v>
-      </c>
-      <c r="P6" t="n">
-        <v>25.83088115666319</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>484.1665533473086</v>
-      </c>
       <c r="R6" t="n">
-        <v>24.12260681035265</v>
+        <v>480.43</v>
       </c>
       <c r="S6" t="n">
-        <v>484.4539188207012</v>
+        <v>28.62</v>
       </c>
       <c r="T6" t="n">
-        <v>23.49428668233225</v>
+        <v>479.42</v>
       </c>
       <c r="U6" t="n">
-        <v>482.5583469452324</v>
+        <v>30.22</v>
       </c>
       <c r="V6" t="n">
-        <v>23.64073097823231</v>
+        <v>482.73</v>
       </c>
       <c r="W6" t="n">
-        <v>481.8439395712294</v>
+        <v>24.31</v>
       </c>
       <c r="X6" t="n">
-        <v>22.63666224667611</v>
+        <v>480.87</v>
       </c>
       <c r="Y6" t="n">
-        <v>479.7778118652919</v>
+        <v>25.83</v>
       </c>
       <c r="Z6" t="n">
-        <v>23.18693402009662</v>
+        <v>484.17</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>24.12</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>484.45</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>23.49</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>482.56</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>23.64</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>481.84</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>22.64</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>479.78</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>23.19</v>
       </c>
       <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
         <v>488.075</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="AT6" t="n">
         <v>484.4833333333333</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AU6" t="n">
         <v>485.225</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="AV6" t="n">
         <v>485.4</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="AW6" t="n">
         <v>484.75</v>
       </c>
-      <c r="AO6" t="n">
+      <c r="AX6" t="n">
         <v>485.25</v>
       </c>
-      <c r="AP6" t="n">
+      <c r="AY6" t="n">
         <v>485.46875</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AZ6" t="n">
         <v>485.4777777777778</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="BA6" t="n">
         <v>485.415</v>
       </c>
-      <c r="AS6" t="n">
+      <c r="BB6" t="n">
         <v>72.82423617862395</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="BC6" t="n">
         <v>63.54145409800509</v>
       </c>
-      <c r="AU6" t="n">
+      <c r="BD6" t="n">
         <v>56.88980027210501</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="BE6" t="n">
         <v>52.47704259959778</v>
       </c>
-      <c r="AW6" t="n">
+      <c r="BF6" t="n">
         <v>49.51687422821975</v>
       </c>
-      <c r="AX6" t="n">
+      <c r="BG6" t="n">
         <v>46.74064077438391</v>
       </c>
-      <c r="AY6" t="n">
+      <c r="BH6" t="n">
         <v>44.7202305834563</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BI6" t="n">
         <v>43.28618660285616</v>
       </c>
-      <c r="BA6" t="n">
+      <c r="BJ6" t="n">
         <v>42.02478762587623</v>
       </c>
-      <c r="BB6" t="n">
+      <c r="BK6" t="n">
         <v>316</v>
       </c>
-      <c r="BC6" t="n">
+      <c r="BL6" t="n">
         <v>316</v>
       </c>
-      <c r="BD6" t="n">
+      <c r="BM6" t="n">
         <v>316</v>
       </c>
-      <c r="BE6" t="n">
+      <c r="BN6" t="n">
         <v>316</v>
       </c>
-      <c r="BF6" t="n">
+      <c r="BO6" t="n">
         <v>316</v>
       </c>
-      <c r="BG6" t="n">
+      <c r="BP6" t="n">
         <v>316</v>
       </c>
-      <c r="BH6" t="n">
+      <c r="BQ6" t="n">
         <v>316</v>
       </c>
-      <c r="BI6" t="n">
+      <c r="BR6" t="n">
         <v>316</v>
       </c>
-      <c r="BJ6" t="n">
+      <c r="BS6" t="n">
         <v>316</v>
       </c>
-      <c r="BK6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>669</v>
-      </c>
       <c r="BT6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC6" t="n">
         <v>0.4545454545454545</v>
       </c>
-      <c r="BU6" t="n">
+      <c r="CD6" t="n">
         <v>0.4761904761904762</v>
       </c>
-      <c r="BV6" t="n">
+      <c r="CE6" t="n">
         <v>0.4838709677419355</v>
       </c>
-      <c r="BW6" t="n">
+      <c r="CF6" t="n">
         <v>0.45</v>
       </c>
-      <c r="BX6" t="n">
+      <c r="CG6" t="n">
         <v>0.4545454545454545</v>
       </c>
-      <c r="BY6" t="n">
+      <c r="CH6" t="n">
         <v>0.02222222222222222</v>
       </c>
-      <c r="BZ6" t="n">
+      <c r="CI6" t="n">
         <v>0.5208333333333334</v>
       </c>
-      <c r="CA6" t="n">
+      <c r="CJ6" t="n">
         <v>0.5660377358490566</v>
       </c>
-      <c r="CB6" t="n">
+      <c r="CK6" t="n">
         <v>0.5964912280701754</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>479.78</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>23.19</v>
       </c>
     </row>
     <row r="7">
@@ -2070,10 +2290,10 @@
         <v>478</v>
       </c>
       <c r="C7" t="n">
+        <v>32.61675315048184</v>
+      </c>
+      <c r="D7" t="n">
         <v>22</v>
-      </c>
-      <c r="D7" t="n">
-        <v>32.61675315048184</v>
       </c>
       <c r="E7" t="n">
         <v>478</v>
@@ -2082,228 +2302,261 @@
         <v>200</v>
       </c>
       <c r="G7" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="H7" t="inlineStr">
+        <v>83</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>450.633420480232</v>
-      </c>
-      <c r="J7" t="n">
-        <v>22.23748964477891</v>
-      </c>
-      <c r="K7" t="n">
-        <v>454.2073950628391</v>
-      </c>
-      <c r="L7" t="n">
-        <v>22.57586351047582</v>
-      </c>
-      <c r="M7" t="n">
-        <v>469.7160712529123</v>
-      </c>
-      <c r="N7" t="n">
-        <v>31.97021795531674</v>
-      </c>
-      <c r="O7" t="n">
-        <v>471.3062537672193</v>
-      </c>
-      <c r="P7" t="n">
-        <v>29.35890362017421</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>468.9241036258099</v>
-      </c>
       <c r="R7" t="n">
-        <v>32.99860984251621</v>
+        <v>450.63</v>
       </c>
       <c r="S7" t="n">
-        <v>468.3300117758714</v>
+        <v>22.24</v>
       </c>
       <c r="T7" t="n">
-        <v>31.77838926272902</v>
+        <v>454.21</v>
       </c>
       <c r="U7" t="n">
-        <v>467.7290570595731</v>
+        <v>22.58</v>
       </c>
       <c r="V7" t="n">
-        <v>31.34844799365433</v>
+        <v>469.72</v>
       </c>
       <c r="W7" t="n">
-        <v>469.6486545607276</v>
+        <v>31.97</v>
       </c>
       <c r="X7" t="n">
-        <v>31.05766664497532</v>
+        <v>471.31</v>
       </c>
       <c r="Y7" t="n">
-        <v>471.3705369011328</v>
+        <v>29.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>31.11166292850985</v>
+        <v>468.92</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>468.33</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>31.78</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>467.73</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>31.35</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>469.65</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>31.06</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>471.37</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>31.11</v>
       </c>
       <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
         <v>479.725</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AT7" t="n">
         <v>475.4333333333333</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AU7" t="n">
         <v>474.2</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AV7" t="n">
         <v>474.52</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AW7" t="n">
         <v>474.6333333333333</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AX7" t="n">
         <v>474.4</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="AY7" t="n">
         <v>474.13125</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AZ7" t="n">
         <v>474.9444444444445</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="BA7" t="n">
         <v>476.215</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="BB7" t="n">
         <v>77.08339234231975</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="BC7" t="n">
         <v>66.81101871863818</v>
       </c>
-      <c r="AU7" t="n">
+      <c r="BD7" t="n">
         <v>61.23426328453704</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="BE7" t="n">
         <v>57.39067520076759</v>
       </c>
-      <c r="AW7" t="n">
+      <c r="BF7" t="n">
         <v>54.59791408306934</v>
       </c>
-      <c r="AX7" t="n">
+      <c r="BG7" t="n">
         <v>52.66576551368884</v>
       </c>
-      <c r="AY7" t="n">
+      <c r="BH7" t="n">
         <v>51.25659980370821</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BI7" t="n">
         <v>49.99452439153514</v>
       </c>
-      <c r="BA7" t="n">
+      <c r="BJ7" t="n">
         <v>48.26923217744405</v>
       </c>
-      <c r="BB7" t="n">
+      <c r="BK7" t="n">
         <v>323</v>
       </c>
-      <c r="BC7" t="n">
+      <c r="BL7" t="n">
         <v>323</v>
       </c>
-      <c r="BD7" t="n">
+      <c r="BM7" t="n">
         <v>323</v>
       </c>
-      <c r="BE7" t="n">
+      <c r="BN7" t="n">
         <v>323</v>
       </c>
-      <c r="BF7" t="n">
+      <c r="BO7" t="n">
         <v>323</v>
       </c>
-      <c r="BG7" t="n">
+      <c r="BP7" t="n">
         <v>323</v>
       </c>
-      <c r="BH7" t="n">
+      <c r="BQ7" t="n">
         <v>323</v>
       </c>
-      <c r="BI7" t="n">
+      <c r="BR7" t="n">
         <v>323</v>
       </c>
-      <c r="BJ7" t="n">
+      <c r="BS7" t="n">
         <v>323</v>
       </c>
-      <c r="BK7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>669</v>
-      </c>
       <c r="BT7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC7" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BU7" t="n">
+      <c r="CD7" t="n">
         <v>0.5294117647058824</v>
       </c>
-      <c r="BV7" t="n">
+      <c r="CE7" t="n">
         <v>0.5416666666666666</v>
       </c>
-      <c r="BW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX7" t="n">
+      <c r="CF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG7" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="BY7" t="n">
+      <c r="CH7" t="n">
         <v>0.6190476190476191</v>
       </c>
-      <c r="BZ7" t="n">
+      <c r="CI7" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="CA7" t="n">
+      <c r="CJ7" t="n">
         <v>0.7916666666666666</v>
       </c>
-      <c r="CB7" t="n">
+      <c r="CK7" t="n">
         <v>0.7037037037037037</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>471.37</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>31.11</v>
       </c>
     </row>
     <row r="8">
@@ -2316,10 +2569,10 @@
         <v>482</v>
       </c>
       <c r="C8" t="n">
+        <v>28.16901408450704</v>
+      </c>
+      <c r="D8" t="n">
         <v>19</v>
-      </c>
-      <c r="D8" t="n">
-        <v>28.16901408450704</v>
       </c>
       <c r="E8" t="n">
         <v>482</v>
@@ -2328,228 +2581,261 @@
         <v>200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="H8" t="inlineStr">
+        <v>83.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>497.8783070766015</v>
-      </c>
-      <c r="J8" t="n">
-        <v>22.56150435385252</v>
-      </c>
-      <c r="K8" t="n">
-        <v>491.2604666740987</v>
-      </c>
-      <c r="L8" t="n">
-        <v>24.67793420259344</v>
-      </c>
-      <c r="M8" t="n">
-        <v>485.9973360825248</v>
-      </c>
-      <c r="N8" t="n">
-        <v>24.63105344771365</v>
-      </c>
-      <c r="O8" t="n">
-        <v>487.4490276439923</v>
-      </c>
-      <c r="P8" t="n">
-        <v>26.0558825009751</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>484.7292941052103</v>
-      </c>
       <c r="R8" t="n">
-        <v>24.17881022190467</v>
+        <v>497.88</v>
       </c>
       <c r="S8" t="n">
-        <v>484.3957695863044</v>
+        <v>22.56</v>
       </c>
       <c r="T8" t="n">
-        <v>23.14223108669964</v>
+        <v>491.26</v>
       </c>
       <c r="U8" t="n">
-        <v>482.8200622551185</v>
+        <v>24.68</v>
       </c>
       <c r="V8" t="n">
-        <v>23.69402999722133</v>
+        <v>486</v>
       </c>
       <c r="W8" t="n">
-        <v>480.857438551008</v>
+        <v>24.63</v>
       </c>
       <c r="X8" t="n">
-        <v>23.00717803516234</v>
+        <v>487.45</v>
       </c>
       <c r="Y8" t="n">
-        <v>480.5397497800512</v>
+        <v>26.06</v>
       </c>
       <c r="Z8" t="n">
-        <v>23.62060366800738</v>
+        <v>484.73</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>24.18</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>484.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>23.14</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>482.82</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>23.69</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>480.86</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>23.01</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>480.54</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>23.62</v>
       </c>
       <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
         <v>497.05</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AT8" t="n">
         <v>496.1</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AU8" t="n">
         <v>493.55</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AV8" t="n">
         <v>491.97</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AW8" t="n">
         <v>490.825</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AX8" t="n">
         <v>489.6071428571428</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AY8" t="n">
         <v>489.10625</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AZ8" t="n">
         <v>488.6222222222222</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="BA8" t="n">
         <v>488.07</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="BB8" t="n">
         <v>69.70937885249015</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="BC8" t="n">
         <v>59.37331050227871</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="BD8" t="n">
         <v>53.73148518327034</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="BE8" t="n">
         <v>49.94425993044646</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="BF8" t="n">
         <v>47.22440444304195</v>
       </c>
-      <c r="AX8" t="n">
+      <c r="BG8" t="n">
         <v>45.39803274979016</v>
       </c>
-      <c r="AY8" t="n">
+      <c r="BH8" t="n">
         <v>43.68475089705217</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BI8" t="n">
         <v>42.02950756519567</v>
       </c>
-      <c r="BA8" t="n">
+      <c r="BJ8" t="n">
         <v>41.0417482571101</v>
       </c>
-      <c r="BB8" t="n">
+      <c r="BK8" t="n">
         <v>323</v>
       </c>
-      <c r="BC8" t="n">
+      <c r="BL8" t="n">
         <v>323</v>
       </c>
-      <c r="BD8" t="n">
+      <c r="BM8" t="n">
         <v>323</v>
       </c>
-      <c r="BE8" t="n">
+      <c r="BN8" t="n">
         <v>323</v>
       </c>
-      <c r="BF8" t="n">
+      <c r="BO8" t="n">
         <v>323</v>
       </c>
-      <c r="BG8" t="n">
+      <c r="BP8" t="n">
         <v>323</v>
       </c>
-      <c r="BH8" t="n">
+      <c r="BQ8" t="n">
         <v>323</v>
       </c>
-      <c r="BI8" t="n">
+      <c r="BR8" t="n">
         <v>323</v>
       </c>
-      <c r="BJ8" t="n">
+      <c r="BS8" t="n">
         <v>323</v>
       </c>
-      <c r="BK8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>669</v>
-      </c>
       <c r="BT8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC8" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="BU8" t="n">
+      <c r="CD8" t="n">
         <v>0.5263157894736842</v>
       </c>
-      <c r="BV8" t="n">
+      <c r="CE8" t="n">
         <v>0.5555555555555556</v>
       </c>
-      <c r="BW8" t="n">
+      <c r="CF8" t="n">
         <v>0.6363636363636364</v>
       </c>
-      <c r="BX8" t="n">
+      <c r="CG8" t="n">
         <v>0.7105263157894737</v>
       </c>
-      <c r="BY8" t="n">
+      <c r="CH8" t="n">
         <v>0.8780487804878049</v>
       </c>
-      <c r="BZ8" t="n">
+      <c r="CI8" t="n">
         <v>0.8913043478260869</v>
       </c>
-      <c r="CA8" t="n">
+      <c r="CJ8" t="n">
         <v>0.9583333333333334</v>
       </c>
-      <c r="CB8" t="n">
+      <c r="CK8" t="n">
         <v>0.9807692307692307</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>480.54</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>23.62</v>
       </c>
     </row>
     <row r="9">
@@ -2562,10 +2848,10 @@
         <v>478</v>
       </c>
       <c r="C9" t="n">
+        <v>26.68643439584878</v>
+      </c>
+      <c r="D9" t="n">
         <v>18</v>
-      </c>
-      <c r="D9" t="n">
-        <v>26.68643439584878</v>
       </c>
       <c r="E9" t="n">
         <v>478</v>
@@ -2574,228 +2860,261 @@
         <v>200</v>
       </c>
       <c r="G9" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="H9" t="inlineStr">
+        <v>83</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>461.1097378474676</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5.15702572607218</v>
-      </c>
-      <c r="K9" t="n">
-        <v>471.8860681857576</v>
-      </c>
-      <c r="L9" t="n">
-        <v>13.43170937602302</v>
-      </c>
-      <c r="M9" t="n">
-        <v>477.0288863710124</v>
-      </c>
-      <c r="N9" t="n">
-        <v>16.05628515419025</v>
-      </c>
-      <c r="O9" t="n">
-        <v>479.8309847416254</v>
-      </c>
-      <c r="P9" t="n">
-        <v>16.24352440764125</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>479.9649893773214</v>
-      </c>
       <c r="R9" t="n">
-        <v>16.70319408100501</v>
+        <v>461.11</v>
       </c>
       <c r="S9" t="n">
-        <v>480.5407625752938</v>
+        <v>5.16</v>
       </c>
       <c r="T9" t="n">
-        <v>17.40359784135877</v>
+        <v>471.89</v>
       </c>
       <c r="U9" t="n">
-        <v>481.3261040593163</v>
+        <v>13.43</v>
       </c>
       <c r="V9" t="n">
-        <v>18.37239977803566</v>
+        <v>477.03</v>
       </c>
       <c r="W9" t="n">
-        <v>480.4679595196204</v>
+        <v>16.06</v>
       </c>
       <c r="X9" t="n">
-        <v>17.44577707370988</v>
+        <v>479.83</v>
       </c>
       <c r="Y9" t="n">
-        <v>481.4793227677814</v>
+        <v>16.24</v>
       </c>
       <c r="Z9" t="n">
-        <v>17.97529222109803</v>
+        <v>479.96</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>480.54</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>17.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>481.33</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>18.37</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>480.47</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>17.45</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>481.48</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>17.98</v>
       </c>
       <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
         <v>490.325</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AT9" t="n">
         <v>487.4333333333333</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AU9" t="n">
         <v>485.6125</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AV9" t="n">
         <v>484.82</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AW9" t="n">
         <v>484.6916666666667</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AX9" t="n">
         <v>484.3071428571429</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AY9" t="n">
         <v>484.40625</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AZ9" t="n">
         <v>484.7666666666667</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="BA9" t="n">
         <v>485.09</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="BB9" t="n">
         <v>67.67731802457897</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="BC9" t="n">
         <v>56.91261332565529</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="BD9" t="n">
         <v>50.83785345340615</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="BE9" t="n">
         <v>46.66055721913316</v>
       </c>
-      <c r="AW9" t="n">
+      <c r="BF9" t="n">
         <v>43.35373798442554</v>
       </c>
-      <c r="AX9" t="n">
+      <c r="BG9" t="n">
         <v>41.04873348117044</v>
       </c>
-      <c r="AY9" t="n">
+      <c r="BH9" t="n">
         <v>39.01767177751</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BI9" t="n">
         <v>37.51860279322187</v>
       </c>
-      <c r="BA9" t="n">
+      <c r="BJ9" t="n">
         <v>36.25812874377276</v>
       </c>
-      <c r="BB9" t="n">
+      <c r="BK9" t="n">
         <v>340</v>
       </c>
-      <c r="BC9" t="n">
+      <c r="BL9" t="n">
         <v>340</v>
       </c>
-      <c r="BD9" t="n">
+      <c r="BM9" t="n">
         <v>340</v>
       </c>
-      <c r="BE9" t="n">
+      <c r="BN9" t="n">
         <v>340</v>
       </c>
-      <c r="BF9" t="n">
+      <c r="BO9" t="n">
         <v>340</v>
       </c>
-      <c r="BG9" t="n">
+      <c r="BP9" t="n">
         <v>340</v>
       </c>
-      <c r="BH9" t="n">
+      <c r="BQ9" t="n">
         <v>340</v>
       </c>
-      <c r="BI9" t="n">
+      <c r="BR9" t="n">
         <v>340</v>
       </c>
-      <c r="BJ9" t="n">
+      <c r="BS9" t="n">
         <v>340</v>
       </c>
-      <c r="BK9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>669</v>
-      </c>
       <c r="BT9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC9" t="n">
         <v>0.9</v>
       </c>
-      <c r="BU9" t="n">
+      <c r="CD9" t="n">
         <v>0.7692307692307693</v>
       </c>
-      <c r="BV9" t="n">
+      <c r="CE9" t="n">
         <v>0.95</v>
       </c>
-      <c r="BW9" t="n">
+      <c r="CF9" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BX9" t="n">
+      <c r="CG9" t="n">
         <v>0.8421052631578947</v>
       </c>
-      <c r="BY9" t="n">
+      <c r="CH9" t="n">
         <v>0.7954545454545454</v>
       </c>
-      <c r="BZ9" t="n">
+      <c r="CI9" t="n">
         <v>0.8367346938775511</v>
       </c>
-      <c r="CA9" t="n">
+      <c r="CJ9" t="n">
         <v>0.9387755102040817</v>
       </c>
-      <c r="CB9" t="n">
+      <c r="CK9" t="n">
         <v>1</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>481.48</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>17.98</v>
       </c>
     </row>
     <row r="10">
@@ -2808,10 +3127,10 @@
         <v>479</v>
       </c>
       <c r="C10" t="n">
+        <v>29.65159377316531</v>
+      </c>
+      <c r="D10" t="n">
         <v>20</v>
-      </c>
-      <c r="D10" t="n">
-        <v>29.65159377316531</v>
       </c>
       <c r="E10" t="n">
         <v>479</v>
@@ -2820,228 +3139,261 @@
         <v>200</v>
       </c>
       <c r="G10" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="H10" t="inlineStr">
+        <v>80</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>488.9446928093341</v>
-      </c>
-      <c r="J10" t="n">
-        <v>25.5368168933935</v>
-      </c>
-      <c r="K10" t="n">
-        <v>477.1457265083855</v>
-      </c>
-      <c r="L10" t="n">
-        <v>23.91918482599181</v>
-      </c>
-      <c r="M10" t="n">
-        <v>473.8008428966916</v>
-      </c>
-      <c r="N10" t="n">
-        <v>23.1215061141883</v>
-      </c>
-      <c r="O10" t="n">
-        <v>479.2942876292425</v>
-      </c>
-      <c r="P10" t="n">
-        <v>24.22268847163413</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>479.3643611013425</v>
-      </c>
       <c r="R10" t="n">
-        <v>25.02032147373087</v>
+        <v>488.94</v>
       </c>
       <c r="S10" t="n">
-        <v>478.8485055361614</v>
+        <v>25.54</v>
       </c>
       <c r="T10" t="n">
-        <v>25.70878959673694</v>
+        <v>477.15</v>
       </c>
       <c r="U10" t="n">
-        <v>478.8982757320749</v>
+        <v>23.92</v>
       </c>
       <c r="V10" t="n">
-        <v>24.31161542720045</v>
+        <v>473.8</v>
       </c>
       <c r="W10" t="n">
-        <v>479.8059314617539</v>
+        <v>23.12</v>
       </c>
       <c r="X10" t="n">
-        <v>26.18105089899768</v>
+        <v>479.29</v>
       </c>
       <c r="Y10" t="n">
-        <v>479.3332917560842</v>
+        <v>24.22</v>
       </c>
       <c r="Z10" t="n">
-        <v>25.43236304665962</v>
+        <v>479.36</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>25.02</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>478.85</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>25.71</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>478.9</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>24.31</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>479.81</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>26.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>479.33</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>25.43</v>
       </c>
       <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
         <v>490.125</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AT10" t="n">
         <v>488.7833333333334</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AU10" t="n">
         <v>487.4125</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AV10" t="n">
         <v>486.79</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AW10" t="n">
         <v>485.575</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AX10" t="n">
         <v>485.0714285714286</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AY10" t="n">
         <v>484.2125</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AZ10" t="n">
         <v>483.7833333333334</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="BA10" t="n">
         <v>483.455</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="BB10" t="n">
         <v>70.70225862728856</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="BC10" t="n">
         <v>60.49300005418441</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="BD10" t="n">
         <v>54.1608008041794</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="BE10" t="n">
         <v>49.75124018554713</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="BF10" t="n">
         <v>47.22687485249615</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="BG10" t="n">
         <v>45.01740026401583</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="BH10" t="n">
         <v>43.43679136112611</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BI10" t="n">
         <v>42.12827962834994</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="BJ10" t="n">
         <v>41.10496289987378</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BK10" t="n">
         <v>327</v>
       </c>
-      <c r="BC10" t="n">
+      <c r="BL10" t="n">
         <v>327</v>
       </c>
-      <c r="BD10" t="n">
+      <c r="BM10" t="n">
         <v>327</v>
       </c>
-      <c r="BE10" t="n">
+      <c r="BN10" t="n">
         <v>327</v>
       </c>
-      <c r="BF10" t="n">
+      <c r="BO10" t="n">
         <v>327</v>
       </c>
-      <c r="BG10" t="n">
+      <c r="BP10" t="n">
         <v>327</v>
       </c>
-      <c r="BH10" t="n">
+      <c r="BQ10" t="n">
         <v>327</v>
       </c>
-      <c r="BI10" t="n">
+      <c r="BR10" t="n">
         <v>327</v>
       </c>
-      <c r="BJ10" t="n">
+      <c r="BS10" t="n">
         <v>327</v>
       </c>
-      <c r="BK10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>669</v>
-      </c>
       <c r="BT10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC10" t="n">
         <v>1</v>
       </c>
-      <c r="BU10" t="n">
+      <c r="CD10" t="n">
         <v>0.9230769230769231</v>
       </c>
-      <c r="BV10" t="n">
+      <c r="CE10" t="n">
         <v>0.6956521739130435</v>
       </c>
-      <c r="BW10" t="n">
+      <c r="CF10" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BX10" t="n">
+      <c r="CG10" t="n">
         <v>0.6976744186046512</v>
       </c>
-      <c r="BY10" t="n">
+      <c r="CH10" t="n">
         <v>0.6792452830188679</v>
       </c>
-      <c r="BZ10" t="n">
+      <c r="CI10" t="n">
         <v>0.6825396825396826</v>
       </c>
-      <c r="CA10" t="n">
+      <c r="CJ10" t="n">
         <v>0.6944444444444444</v>
       </c>
-      <c r="CB10" t="n">
+      <c r="CK10" t="n">
         <v>0.6707317073170732</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>479.33</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>25.43</v>
       </c>
     </row>
     <row r="11">
@@ -3054,10 +3406,10 @@
         <v>480</v>
       </c>
       <c r="C11" t="n">
+        <v>28.16901408450704</v>
+      </c>
+      <c r="D11" t="n">
         <v>19</v>
-      </c>
-      <c r="D11" t="n">
-        <v>28.16901408450704</v>
       </c>
       <c r="E11" t="n">
         <v>480</v>
@@ -3066,228 +3418,261 @@
         <v>200</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="H11" t="inlineStr">
+        <v>83</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>473.4591059202011</v>
-      </c>
-      <c r="J11" t="n">
-        <v>21.19707046404247</v>
-      </c>
-      <c r="K11" t="n">
-        <v>478.8082812319179</v>
-      </c>
-      <c r="L11" t="n">
-        <v>22.1108857728493</v>
-      </c>
-      <c r="M11" t="n">
-        <v>478.6100491000818</v>
-      </c>
-      <c r="N11" t="n">
-        <v>21.19946323814019</v>
-      </c>
-      <c r="O11" t="n">
-        <v>483.1181652382613</v>
-      </c>
-      <c r="P11" t="n">
-        <v>23.78298054664674</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>482.2186386300242</v>
-      </c>
       <c r="R11" t="n">
-        <v>21.64776949871743</v>
+        <v>473.46</v>
       </c>
       <c r="S11" t="n">
-        <v>481.7789658994319</v>
+        <v>21.2</v>
       </c>
       <c r="T11" t="n">
-        <v>22.40336382853674</v>
+        <v>478.81</v>
       </c>
       <c r="U11" t="n">
-        <v>480.7301979561828</v>
+        <v>22.11</v>
       </c>
       <c r="V11" t="n">
-        <v>20.98092293163291</v>
+        <v>478.61</v>
       </c>
       <c r="W11" t="n">
-        <v>479.1183464519405</v>
+        <v>21.2</v>
       </c>
       <c r="X11" t="n">
-        <v>20.11421869437943</v>
+        <v>483.12</v>
       </c>
       <c r="Y11" t="n">
-        <v>477.5015357748441</v>
+        <v>23.78</v>
       </c>
       <c r="Z11" t="n">
-        <v>20.91181801163181</v>
+        <v>482.22</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>21.65</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>481.78</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>22.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>480.73</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>20.98</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>479.12</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>20.11</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>477.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>20.91</v>
       </c>
       <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
         <v>492.225</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AT11" t="n">
         <v>487.7833333333334</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AU11" t="n">
         <v>486.5875</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AV11" t="n">
         <v>485.95</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AW11" t="n">
         <v>486.3583333333333</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="AX11" t="n">
         <v>485.9071428571428</v>
       </c>
-      <c r="AP11" t="n">
+      <c r="AY11" t="n">
         <v>485.59375</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AZ11" t="n">
         <v>485.2</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="BA11" t="n">
         <v>484.75</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="BB11" t="n">
         <v>68.11845840152286</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="BC11" t="n">
         <v>58.33383571212242</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="BD11" t="n">
         <v>52.14299899075618</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="BE11" t="n">
         <v>48.09768705457675</v>
       </c>
-      <c r="AW11" t="n">
+      <c r="BF11" t="n">
         <v>45.05363393285336</v>
       </c>
-      <c r="AX11" t="n">
+      <c r="BG11" t="n">
         <v>43.15816367544772</v>
       </c>
-      <c r="AY11" t="n">
+      <c r="BH11" t="n">
         <v>41.34720318156356</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BI11" t="n">
         <v>40.05335330669719</v>
       </c>
-      <c r="BA11" t="n">
+      <c r="BJ11" t="n">
         <v>38.95661047883915</v>
       </c>
-      <c r="BB11" t="n">
+      <c r="BK11" t="n">
         <v>343</v>
       </c>
-      <c r="BC11" t="n">
+      <c r="BL11" t="n">
         <v>343</v>
       </c>
-      <c r="BD11" t="n">
+      <c r="BM11" t="n">
         <v>343</v>
       </c>
-      <c r="BE11" t="n">
+      <c r="BN11" t="n">
         <v>343</v>
       </c>
-      <c r="BF11" t="n">
+      <c r="BO11" t="n">
         <v>343</v>
       </c>
-      <c r="BG11" t="n">
+      <c r="BP11" t="n">
         <v>343</v>
       </c>
-      <c r="BH11" t="n">
+      <c r="BQ11" t="n">
         <v>343</v>
       </c>
-      <c r="BI11" t="n">
+      <c r="BR11" t="n">
         <v>343</v>
       </c>
-      <c r="BJ11" t="n">
+      <c r="BS11" t="n">
         <v>343</v>
       </c>
-      <c r="BK11" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>669</v>
-      </c>
       <c r="BT11" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC11" t="n">
         <v>0.7</v>
       </c>
-      <c r="BU11" t="n">
+      <c r="CD11" t="n">
         <v>0.9411764705882353</v>
       </c>
-      <c r="BV11" t="n">
+      <c r="CE11" t="n">
         <v>0.9583333333333334</v>
       </c>
-      <c r="BW11" t="n">
+      <c r="CF11" t="n">
         <v>0.8</v>
       </c>
-      <c r="BX11" t="n">
+      <c r="CG11" t="n">
         <v>0.65</v>
       </c>
-      <c r="BY11" t="n">
+      <c r="CH11" t="n">
         <v>0.574468085106383</v>
       </c>
-      <c r="BZ11" t="n">
+      <c r="CI11" t="n">
         <v>0.6078431372549019</v>
       </c>
-      <c r="CA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB11" t="n">
+      <c r="CJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK11" t="n">
         <v>0.6229508196721312</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>477.5</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>20.91</v>
       </c>
     </row>
     <row r="12">
@@ -3300,10 +3685,10 @@
         <v>481</v>
       </c>
       <c r="C12" t="n">
+        <v>26.68643439584878</v>
+      </c>
+      <c r="D12" t="n">
         <v>18</v>
-      </c>
-      <c r="D12" t="n">
-        <v>26.68643439584878</v>
       </c>
       <c r="E12" t="n">
         <v>481</v>
@@ -3312,228 +3697,261 @@
         <v>200</v>
       </c>
       <c r="G12" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="H12" t="inlineStr">
+        <v>84.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>484.8619893375993</v>
-      </c>
-      <c r="J12" t="n">
-        <v>28.96052939593528</v>
-      </c>
-      <c r="K12" t="n">
-        <v>479.7207389707081</v>
-      </c>
-      <c r="L12" t="n">
-        <v>22.84163272905556</v>
-      </c>
-      <c r="M12" t="n">
-        <v>474.1647130097495</v>
-      </c>
-      <c r="N12" t="n">
-        <v>22.02894078949713</v>
-      </c>
-      <c r="O12" t="n">
-        <v>474.1307792963115</v>
-      </c>
-      <c r="P12" t="n">
-        <v>23.23418459635047</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>471.4636738432645</v>
-      </c>
       <c r="R12" t="n">
-        <v>23.20565882982339</v>
+        <v>484.86</v>
       </c>
       <c r="S12" t="n">
-        <v>469.6115018502222</v>
+        <v>28.96</v>
       </c>
       <c r="T12" t="n">
-        <v>23.19307492926407</v>
+        <v>479.72</v>
       </c>
       <c r="U12" t="n">
-        <v>474.0962517855118</v>
+        <v>22.84</v>
       </c>
       <c r="V12" t="n">
-        <v>23.92341074017739</v>
+        <v>474.16</v>
       </c>
       <c r="W12" t="n">
-        <v>474.3442430833226</v>
+        <v>22.03</v>
       </c>
       <c r="X12" t="n">
-        <v>23.67975559625581</v>
+        <v>474.13</v>
       </c>
       <c r="Y12" t="n">
-        <v>475.4160870216252</v>
+        <v>23.23</v>
       </c>
       <c r="Z12" t="n">
-        <v>21.9643719488689</v>
+        <v>471.46</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>23.21</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>469.61</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>23.19</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>474.1</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>23.92</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>474.34</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>23.68</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>475.42</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>21.96</v>
       </c>
       <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
         <v>487.95</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AT12" t="n">
         <v>486.2166666666666</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AU12" t="n">
         <v>485.4</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AV12" t="n">
         <v>484.21</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AW12" t="n">
         <v>483.3833333333333</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AX12" t="n">
         <v>482.6714285714286</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AY12" t="n">
         <v>482.475</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AZ12" t="n">
         <v>482.4722222222222</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="BA12" t="n">
         <v>482.52</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="BB12" t="n">
         <v>75.26119518051783</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="BC12" t="n">
         <v>64.7747614601723</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="BD12" t="n">
         <v>57.41114874307951</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="BE12" t="n">
         <v>52.88445801934629</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="BF12" t="n">
         <v>49.66239075553608</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="BG12" t="n">
         <v>47.2043343737995</v>
       </c>
-      <c r="AY12" t="n">
+      <c r="BH12" t="n">
         <v>45.30148314349101</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BI12" t="n">
         <v>43.91917204182595</v>
       </c>
-      <c r="BA12" t="n">
+      <c r="BJ12" t="n">
         <v>42.49740697972054</v>
       </c>
-      <c r="BB12" t="n">
+      <c r="BK12" t="n">
         <v>318</v>
       </c>
-      <c r="BC12" t="n">
+      <c r="BL12" t="n">
         <v>318</v>
       </c>
-      <c r="BD12" t="n">
+      <c r="BM12" t="n">
         <v>318</v>
       </c>
-      <c r="BE12" t="n">
+      <c r="BN12" t="n">
         <v>318</v>
       </c>
-      <c r="BF12" t="n">
+      <c r="BO12" t="n">
         <v>318</v>
       </c>
-      <c r="BG12" t="n">
+      <c r="BP12" t="n">
         <v>318</v>
       </c>
-      <c r="BH12" t="n">
+      <c r="BQ12" t="n">
         <v>318</v>
       </c>
-      <c r="BI12" t="n">
+      <c r="BR12" t="n">
         <v>318</v>
       </c>
-      <c r="BJ12" t="n">
+      <c r="BS12" t="n">
         <v>318</v>
       </c>
-      <c r="BK12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>669</v>
-      </c>
       <c r="BT12" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC12" t="n">
         <v>0.7</v>
       </c>
-      <c r="BU12" t="n">
+      <c r="CD12" t="n">
         <v>0.8666666666666667</v>
       </c>
-      <c r="BV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW12" t="n">
+      <c r="CE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF12" t="n">
         <v>1</v>
       </c>
-      <c r="BX12" t="n">
+      <c r="CG12" t="n">
         <v>0.8064516129032258</v>
       </c>
-      <c r="BY12" t="n">
+      <c r="CH12" t="n">
         <v>0.7317073170731707</v>
       </c>
-      <c r="BZ12" t="n">
+      <c r="CI12" t="n">
         <v>0.76</v>
       </c>
-      <c r="CA12" t="n">
+      <c r="CJ12" t="n">
         <v>0.8490566037735849</v>
       </c>
-      <c r="CB12" t="n">
+      <c r="CK12" t="n">
         <v>0.8095238095238095</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>475.42</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>21.96</v>
       </c>
     </row>
     <row r="13">
@@ -3546,10 +3964,10 @@
         <v>479</v>
       </c>
       <c r="C13" t="n">
+        <v>28.16901408450704</v>
+      </c>
+      <c r="D13" t="n">
         <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>28.16901408450704</v>
       </c>
       <c r="E13" t="n">
         <v>479</v>
@@ -3558,228 +3976,261 @@
         <v>200</v>
       </c>
       <c r="G13" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="H13" t="inlineStr">
+        <v>83.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>466.8835511175283</v>
-      </c>
-      <c r="J13" t="n">
-        <v>21.16054604492874</v>
-      </c>
-      <c r="K13" t="n">
-        <v>484.2939997956383</v>
-      </c>
-      <c r="L13" t="n">
-        <v>22.81333152751525</v>
-      </c>
-      <c r="M13" t="n">
-        <v>479.4816791688983</v>
-      </c>
-      <c r="N13" t="n">
-        <v>20.02916011814673</v>
-      </c>
-      <c r="O13" t="n">
-        <v>479.6177847229553</v>
-      </c>
-      <c r="P13" t="n">
-        <v>20.83975676083483</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>476.4504516037839</v>
-      </c>
       <c r="R13" t="n">
-        <v>21.78491332678809</v>
+        <v>466.88</v>
       </c>
       <c r="S13" t="n">
-        <v>479.5345654478216</v>
+        <v>21.16</v>
       </c>
       <c r="T13" t="n">
-        <v>22.58180620005646</v>
+        <v>484.29</v>
       </c>
       <c r="U13" t="n">
-        <v>478.6349265582428</v>
+        <v>22.81</v>
       </c>
       <c r="V13" t="n">
-        <v>21.34752839166175</v>
+        <v>479.48</v>
       </c>
       <c r="W13" t="n">
-        <v>479.0360344012751</v>
+        <v>20.03</v>
       </c>
       <c r="X13" t="n">
-        <v>19.74851317105716</v>
+        <v>479.62</v>
       </c>
       <c r="Y13" t="n">
-        <v>478.63840030438</v>
+        <v>20.84</v>
       </c>
       <c r="Z13" t="n">
-        <v>19.39126982538319</v>
+        <v>476.45</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>21.78</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>479.53</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>22.58</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>478.63</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>21.35</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>479.04</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>19.75</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>478.64</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>19.39</v>
       </c>
       <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
         <v>481.475</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AT13" t="n">
         <v>482.2</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AU13" t="n">
         <v>483.1</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AV13" t="n">
         <v>483.42</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AW13" t="n">
         <v>483.0166666666667</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AX13" t="n">
         <v>483.7285714285715</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="AY13" t="n">
         <v>484.35625</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AZ13" t="n">
         <v>484.4055555555556</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="BA13" t="n">
         <v>484.435</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="BB13" t="n">
         <v>74.22734923867348</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="BC13" t="n">
         <v>62.9316560510951</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="BD13" t="n">
         <v>55.94877121081392</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="BE13" t="n">
         <v>51.03002645501959</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="BF13" t="n">
         <v>47.92041724452</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="BG13" t="n">
         <v>45.26254251698683</v>
       </c>
-      <c r="AY13" t="n">
+      <c r="BH13" t="n">
         <v>43.35728699927499</v>
       </c>
-      <c r="AZ13" t="n">
+      <c r="BI13" t="n">
         <v>41.60751764635038</v>
       </c>
-      <c r="BA13" t="n">
+      <c r="BJ13" t="n">
         <v>40.12986138774965</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BK13" t="n">
         <v>330</v>
       </c>
-      <c r="BC13" t="n">
+      <c r="BL13" t="n">
         <v>330</v>
       </c>
-      <c r="BD13" t="n">
+      <c r="BM13" t="n">
         <v>330</v>
       </c>
-      <c r="BE13" t="n">
+      <c r="BN13" t="n">
         <v>330</v>
       </c>
-      <c r="BF13" t="n">
+      <c r="BO13" t="n">
         <v>330</v>
       </c>
-      <c r="BG13" t="n">
+      <c r="BP13" t="n">
         <v>330</v>
       </c>
-      <c r="BH13" t="n">
+      <c r="BQ13" t="n">
         <v>330</v>
       </c>
-      <c r="BI13" t="n">
+      <c r="BR13" t="n">
         <v>330</v>
       </c>
-      <c r="BJ13" t="n">
+      <c r="BS13" t="n">
         <v>330</v>
       </c>
-      <c r="BK13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>669</v>
-      </c>
       <c r="BT13" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC13" t="n">
         <v>1</v>
       </c>
-      <c r="BU13" t="n">
+      <c r="CD13" t="n">
         <v>0.5294117647058824</v>
       </c>
-      <c r="BV13" t="n">
+      <c r="CE13" t="n">
         <v>0.4074074074074074</v>
       </c>
-      <c r="BW13" t="n">
+      <c r="CF13" t="n">
         <v>0.4324324324324325</v>
       </c>
-      <c r="BX13" t="n">
+      <c r="CG13" t="n">
         <v>0.425531914893617</v>
       </c>
-      <c r="BY13" t="n">
+      <c r="CH13" t="n">
         <v>0.4642857142857143</v>
       </c>
-      <c r="BZ13" t="n">
+      <c r="CI13" t="n">
         <v>0.4461538461538462</v>
       </c>
-      <c r="CA13" t="n">
+      <c r="CJ13" t="n">
         <v>0.4666666666666667</v>
       </c>
-      <c r="CB13" t="n">
+      <c r="CK13" t="n">
         <v>0.4941176470588236</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>478.64</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>19.39</v>
       </c>
     </row>
     <row r="14">
@@ -3792,10 +4243,10 @@
         <v>480</v>
       </c>
       <c r="C14" t="n">
+        <v>31.13417346182357</v>
+      </c>
+      <c r="D14" t="n">
         <v>21</v>
-      </c>
-      <c r="D14" t="n">
-        <v>31.13417346182357</v>
       </c>
       <c r="E14" t="n">
         <v>480</v>
@@ -3804,228 +4255,261 @@
         <v>200</v>
       </c>
       <c r="G14" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="H14" t="inlineStr">
+        <v>83.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>473.2913022807826</v>
-      </c>
-      <c r="J14" t="n">
-        <v>22.68628982130582</v>
-      </c>
-      <c r="K14" t="n">
-        <v>482.2958533298158</v>
-      </c>
-      <c r="L14" t="n">
-        <v>23.79505099472104</v>
-      </c>
-      <c r="M14" t="n">
-        <v>486.835999431357</v>
-      </c>
-      <c r="N14" t="n">
-        <v>25.59141453891695</v>
-      </c>
-      <c r="O14" t="n">
-        <v>480.5209559462268</v>
-      </c>
-      <c r="P14" t="n">
-        <v>24.47227336991985</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>482.0939542236438</v>
-      </c>
       <c r="R14" t="n">
-        <v>23.72299281411513</v>
+        <v>473.29</v>
       </c>
       <c r="S14" t="n">
-        <v>486.5859013472015</v>
+        <v>22.69</v>
       </c>
       <c r="T14" t="n">
-        <v>27.44003977652811</v>
+        <v>482.3</v>
       </c>
       <c r="U14" t="n">
-        <v>484.5414327954111</v>
+        <v>23.8</v>
       </c>
       <c r="V14" t="n">
-        <v>26.64970506448386</v>
+        <v>486.84</v>
       </c>
       <c r="W14" t="n">
-        <v>486.527808930526</v>
+        <v>25.59</v>
       </c>
       <c r="X14" t="n">
-        <v>26.14343688104139</v>
+        <v>480.52</v>
       </c>
       <c r="Y14" t="n">
-        <v>484.6348555884287</v>
+        <v>24.47</v>
       </c>
       <c r="Z14" t="n">
-        <v>25.48750651473839</v>
+        <v>482.09</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>23.72</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>486.59</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>27.44</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>484.54</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>26.65</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>486.53</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>26.14</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>484.63</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>25.49</v>
       </c>
       <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
         <v>486.15</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AT14" t="n">
         <v>484.8333333333333</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="AU14" t="n">
         <v>485.5875</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="AV14" t="n">
         <v>484.86</v>
       </c>
-      <c r="AN14" t="n">
+      <c r="AW14" t="n">
         <v>485.55</v>
       </c>
-      <c r="AO14" t="n">
+      <c r="AX14" t="n">
         <v>485.9571428571429</v>
       </c>
-      <c r="AP14" t="n">
+      <c r="AY14" t="n">
         <v>486.94375</v>
       </c>
-      <c r="AQ14" t="n">
+      <c r="AZ14" t="n">
         <v>486.7777777777778</v>
       </c>
-      <c r="AR14" t="n">
+      <c r="BA14" t="n">
         <v>486.97</v>
       </c>
-      <c r="AS14" t="n">
+      <c r="BB14" t="n">
         <v>73.42429774945076</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="BC14" t="n">
         <v>62.99925043645801</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="BD14" t="n">
         <v>56.47913193162587</v>
       </c>
-      <c r="AV14" t="n">
+      <c r="BE14" t="n">
         <v>52.40572869448531</v>
       </c>
-      <c r="AW14" t="n">
+      <c r="BF14" t="n">
         <v>50.13030520553411</v>
       </c>
-      <c r="AX14" t="n">
+      <c r="BG14" t="n">
         <v>48.2429671304639</v>
       </c>
-      <c r="AY14" t="n">
+      <c r="BH14" t="n">
         <v>46.73398748167654</v>
       </c>
-      <c r="AZ14" t="n">
+      <c r="BI14" t="n">
         <v>45.18376743373855</v>
       </c>
-      <c r="BA14" t="n">
+      <c r="BJ14" t="n">
         <v>43.66576576678806</v>
       </c>
-      <c r="BB14" t="n">
+      <c r="BK14" t="n">
         <v>332</v>
       </c>
-      <c r="BC14" t="n">
+      <c r="BL14" t="n">
         <v>332</v>
       </c>
-      <c r="BD14" t="n">
+      <c r="BM14" t="n">
         <v>332</v>
       </c>
-      <c r="BE14" t="n">
+      <c r="BN14" t="n">
         <v>332</v>
       </c>
-      <c r="BF14" t="n">
+      <c r="BO14" t="n">
         <v>332</v>
       </c>
-      <c r="BG14" t="n">
+      <c r="BP14" t="n">
         <v>332</v>
       </c>
-      <c r="BH14" t="n">
+      <c r="BQ14" t="n">
         <v>332</v>
       </c>
-      <c r="BI14" t="n">
+      <c r="BR14" t="n">
         <v>332</v>
       </c>
-      <c r="BJ14" t="n">
+      <c r="BS14" t="n">
         <v>332</v>
       </c>
-      <c r="BK14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>669</v>
-      </c>
       <c r="BT14" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BU14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD14" t="n">
         <v>0.75</v>
       </c>
-      <c r="BV14" t="n">
+      <c r="CE14" t="n">
         <v>0.7894736842105263</v>
       </c>
-      <c r="BW14" t="n">
+      <c r="CF14" t="n">
         <v>0.6896551724137931</v>
       </c>
-      <c r="BX14" t="n">
+      <c r="CG14" t="n">
         <v>0.8666666666666667</v>
       </c>
-      <c r="BY14" t="n">
+      <c r="CH14" t="n">
         <v>0.8823529411764706</v>
       </c>
-      <c r="BZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA14" t="n">
+      <c r="CI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ14" t="n">
         <v>0.9761904761904762</v>
       </c>
-      <c r="CB14" t="n">
+      <c r="CK14" t="n">
         <v>0.8461538461538461</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>484.63</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>25.49</v>
       </c>
     </row>
     <row r="15">
@@ -4038,10 +4522,10 @@
         <v>478</v>
       </c>
       <c r="C15" t="n">
+        <v>29.65159377316531</v>
+      </c>
+      <c r="D15" t="n">
         <v>20</v>
-      </c>
-      <c r="D15" t="n">
-        <v>29.65159377316531</v>
       </c>
       <c r="E15" t="n">
         <v>478</v>
@@ -4050,228 +4534,261 @@
         <v>200</v>
       </c>
       <c r="G15" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="H15" t="inlineStr">
+        <v>82.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>464.9216914814335</v>
-      </c>
-      <c r="J15" t="n">
-        <v>23.53583700637486</v>
-      </c>
-      <c r="K15" t="n">
-        <v>467.3088757884765</v>
-      </c>
-      <c r="L15" t="n">
-        <v>24.94190217221125</v>
-      </c>
-      <c r="M15" t="n">
-        <v>467.7691595587409</v>
-      </c>
-      <c r="N15" t="n">
-        <v>24.91396099227134</v>
-      </c>
-      <c r="O15" t="n">
-        <v>471.6175029341777</v>
-      </c>
-      <c r="P15" t="n">
-        <v>24.85493296584701</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>470.4489836308994</v>
-      </c>
       <c r="R15" t="n">
-        <v>25.08894883158259</v>
+        <v>464.92</v>
       </c>
       <c r="S15" t="n">
-        <v>469.7235929206237</v>
+        <v>23.54</v>
       </c>
       <c r="T15" t="n">
-        <v>24.42375901776325</v>
+        <v>467.31</v>
       </c>
       <c r="U15" t="n">
-        <v>469.0184520267842</v>
+        <v>24.94</v>
       </c>
       <c r="V15" t="n">
-        <v>24.35172037636127</v>
+        <v>467.77</v>
       </c>
       <c r="W15" t="n">
-        <v>472.19618543957</v>
+        <v>24.91</v>
       </c>
       <c r="X15" t="n">
-        <v>24.84073232658884</v>
+        <v>471.62</v>
       </c>
       <c r="Y15" t="n">
-        <v>472.8523847165324</v>
+        <v>24.85</v>
       </c>
       <c r="Z15" t="n">
-        <v>24.73156717045456</v>
+        <v>470.45</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>25.09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>469.72</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>24.42</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>469.02</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>24.35</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>472.2</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>24.84</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>472.85</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>24.73</v>
       </c>
       <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
         <v>491.05</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AT15" t="n">
         <v>486.5166666666667</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AU15" t="n">
         <v>483.775</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="AV15" t="n">
         <v>482.19</v>
       </c>
-      <c r="AN15" t="n">
+      <c r="AW15" t="n">
         <v>480.2916666666667</v>
       </c>
-      <c r="AO15" t="n">
+      <c r="AX15" t="n">
         <v>479.95</v>
       </c>
-      <c r="AP15" t="n">
+      <c r="AY15" t="n">
         <v>478.8125</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="AZ15" t="n">
         <v>479.2944444444444</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="BA15" t="n">
         <v>479.505</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="BB15" t="n">
         <v>70.07779605552675</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="BC15" t="n">
         <v>61.29586491400179</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="BD15" t="n">
         <v>55.82270483414432</v>
       </c>
-      <c r="AV15" t="n">
+      <c r="BE15" t="n">
         <v>51.88346461060595</v>
       </c>
-      <c r="AW15" t="n">
+      <c r="BF15" t="n">
         <v>49.80953654226825</v>
       </c>
-      <c r="AX15" t="n">
+      <c r="BG15" t="n">
         <v>47.30287291184634</v>
       </c>
-      <c r="AY15" t="n">
+      <c r="BH15" t="n">
         <v>45.95720665738943</v>
       </c>
-      <c r="AZ15" t="n">
+      <c r="BI15" t="n">
         <v>43.9398196049276</v>
       </c>
-      <c r="BA15" t="n">
+      <c r="BJ15" t="n">
         <v>42.76458786192146</v>
       </c>
-      <c r="BB15" t="n">
+      <c r="BK15" t="n">
         <v>338</v>
       </c>
-      <c r="BC15" t="n">
+      <c r="BL15" t="n">
         <v>338</v>
       </c>
-      <c r="BD15" t="n">
+      <c r="BM15" t="n">
         <v>338</v>
       </c>
-      <c r="BE15" t="n">
+      <c r="BN15" t="n">
         <v>338</v>
       </c>
-      <c r="BF15" t="n">
+      <c r="BO15" t="n">
         <v>338</v>
       </c>
-      <c r="BG15" t="n">
+      <c r="BP15" t="n">
         <v>338</v>
       </c>
-      <c r="BH15" t="n">
+      <c r="BQ15" t="n">
         <v>338</v>
       </c>
-      <c r="BI15" t="n">
+      <c r="BR15" t="n">
         <v>338</v>
       </c>
-      <c r="BJ15" t="n">
+      <c r="BS15" t="n">
         <v>338</v>
       </c>
-      <c r="BK15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>669</v>
-      </c>
       <c r="BT15" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC15" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BU15" t="n">
+      <c r="CD15" t="n">
         <v>0.7333333333333333</v>
       </c>
-      <c r="BV15" t="n">
+      <c r="CE15" t="n">
         <v>0.68</v>
       </c>
-      <c r="BW15" t="n">
+      <c r="CF15" t="n">
         <v>0.6857142857142857</v>
       </c>
-      <c r="BX15" t="n">
+      <c r="CG15" t="n">
         <v>0.6444444444444445</v>
       </c>
-      <c r="BY15" t="n">
+      <c r="CH15" t="n">
         <v>0.6</v>
       </c>
-      <c r="BZ15" t="n">
+      <c r="CI15" t="n">
         <v>0.6166666666666667</v>
       </c>
-      <c r="CA15" t="n">
+      <c r="CJ15" t="n">
         <v>0.6</v>
       </c>
-      <c r="CB15" t="n">
+      <c r="CK15" t="n">
         <v>0.5466666666666666</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>472.85</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>24.73</v>
       </c>
     </row>
     <row r="16">
@@ -4284,10 +4801,10 @@
         <v>480</v>
       </c>
       <c r="C16" t="n">
+        <v>26.68643439584878</v>
+      </c>
+      <c r="D16" t="n">
         <v>18</v>
-      </c>
-      <c r="D16" t="n">
-        <v>26.68643439584878</v>
       </c>
       <c r="E16" t="n">
         <v>480</v>
@@ -4296,228 +4813,261 @@
         <v>200</v>
       </c>
       <c r="G16" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="H16" t="inlineStr">
+        <v>81.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>484.0238232770052</v>
-      </c>
-      <c r="J16" t="n">
-        <v>19.36079045605478</v>
-      </c>
-      <c r="K16" t="n">
-        <v>485.6824230182809</v>
-      </c>
-      <c r="L16" t="n">
-        <v>20.61201767937712</v>
-      </c>
-      <c r="M16" t="n">
-        <v>483.4805937167213</v>
-      </c>
-      <c r="N16" t="n">
-        <v>19.74960569000685</v>
-      </c>
-      <c r="O16" t="n">
-        <v>480.2296930910198</v>
-      </c>
-      <c r="P16" t="n">
-        <v>17.63559373111724</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>476.9818169913207</v>
-      </c>
       <c r="R16" t="n">
-        <v>16.807779303753</v>
+        <v>484.02</v>
       </c>
       <c r="S16" t="n">
-        <v>475.5514223852547</v>
+        <v>19.36</v>
       </c>
       <c r="T16" t="n">
-        <v>17.04460067420509</v>
+        <v>485.68</v>
       </c>
       <c r="U16" t="n">
-        <v>476.625746858867</v>
+        <v>20.61</v>
       </c>
       <c r="V16" t="n">
-        <v>19.42648309903063</v>
+        <v>483.48</v>
       </c>
       <c r="W16" t="n">
-        <v>476.1690051341288</v>
+        <v>19.75</v>
       </c>
       <c r="X16" t="n">
-        <v>19.54592951945621</v>
+        <v>480.23</v>
       </c>
       <c r="Y16" t="n">
-        <v>474.8597192725003</v>
+        <v>17.64</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.66638377502638</v>
+        <v>476.98</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>16.81</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>475.55</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>17.04</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>476.63</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>19.43</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>476.17</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>19.55</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>474.86</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>19.67</v>
       </c>
       <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
         <v>496.775</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AT16" t="n">
         <v>493.35</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AU16" t="n">
         <v>492.25</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="AV16" t="n">
         <v>490.85</v>
       </c>
-      <c r="AN16" t="n">
+      <c r="AW16" t="n">
         <v>489.5583333333333</v>
       </c>
-      <c r="AO16" t="n">
+      <c r="AX16" t="n">
         <v>488.4428571428571</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="AY16" t="n">
         <v>487.64375</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AZ16" t="n">
         <v>487.0777777777778</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="BA16" t="n">
         <v>486.19</v>
       </c>
-      <c r="AS16" t="n">
+      <c r="BB16" t="n">
         <v>69.76155370259467</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="BC16" t="n">
         <v>58.88769679086909</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="BD16" t="n">
         <v>52.43007247753907</v>
       </c>
-      <c r="AV16" t="n">
+      <c r="BE16" t="n">
         <v>47.98799328998869</v>
       </c>
-      <c r="AW16" t="n">
+      <c r="BF16" t="n">
         <v>44.72150784453594</v>
       </c>
-      <c r="AX16" t="n">
+      <c r="BG16" t="n">
         <v>42.22766043865619</v>
       </c>
-      <c r="AY16" t="n">
+      <c r="BH16" t="n">
         <v>40.25828282400406</v>
       </c>
-      <c r="AZ16" t="n">
+      <c r="BI16" t="n">
         <v>38.75872024540708</v>
       </c>
-      <c r="BA16" t="n">
+      <c r="BJ16" t="n">
         <v>37.85107528195203</v>
       </c>
-      <c r="BB16" t="n">
+      <c r="BK16" t="n">
         <v>320</v>
       </c>
-      <c r="BC16" t="n">
+      <c r="BL16" t="n">
         <v>320</v>
       </c>
-      <c r="BD16" t="n">
+      <c r="BM16" t="n">
         <v>320</v>
       </c>
-      <c r="BE16" t="n">
+      <c r="BN16" t="n">
         <v>320</v>
       </c>
-      <c r="BF16" t="n">
+      <c r="BO16" t="n">
         <v>320</v>
       </c>
-      <c r="BG16" t="n">
+      <c r="BP16" t="n">
         <v>320</v>
       </c>
-      <c r="BH16" t="n">
+      <c r="BQ16" t="n">
         <v>320</v>
       </c>
-      <c r="BI16" t="n">
+      <c r="BR16" t="n">
         <v>320</v>
       </c>
-      <c r="BJ16" t="n">
+      <c r="BS16" t="n">
         <v>320</v>
       </c>
-      <c r="BK16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>669</v>
-      </c>
       <c r="BT16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC16" t="n">
         <v>0.875</v>
       </c>
-      <c r="BU16" t="n">
+      <c r="CD16" t="n">
         <v>0.6428571428571429</v>
       </c>
-      <c r="BV16" t="n">
+      <c r="CE16" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BW16" t="n">
+      <c r="CF16" t="n">
         <v>0.8214285714285714</v>
       </c>
-      <c r="BX16" t="n">
+      <c r="CG16" t="n">
         <v>0.9705882352941176</v>
       </c>
-      <c r="BY16" t="n">
+      <c r="CH16" t="n">
         <v>0.9302325581395349</v>
       </c>
-      <c r="BZ16" t="n">
+      <c r="CI16" t="n">
         <v>0.8679245283018868</v>
       </c>
-      <c r="CA16" t="n">
+      <c r="CJ16" t="n">
         <v>0.8095238095238095</v>
       </c>
-      <c r="CB16" t="n">
+      <c r="CK16" t="n">
         <v>0.7534246575342466</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>474.86</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>19.67</v>
       </c>
     </row>
     <row r="17">
@@ -4530,10 +5080,10 @@
         <v>481</v>
       </c>
       <c r="C17" t="n">
+        <v>26.68643439584878</v>
+      </c>
+      <c r="D17" t="n">
         <v>18</v>
-      </c>
-      <c r="D17" t="n">
-        <v>26.68643439584878</v>
       </c>
       <c r="E17" t="n">
         <v>481</v>
@@ -4542,228 +5092,261 @@
         <v>200</v>
       </c>
       <c r="G17" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="H17" t="inlineStr">
+        <v>83</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>474.8501927848723</v>
-      </c>
-      <c r="J17" t="n">
-        <v>19.83208295109199</v>
-      </c>
-      <c r="K17" t="n">
-        <v>475.6376451582818</v>
-      </c>
-      <c r="L17" t="n">
-        <v>19.17930230556229</v>
-      </c>
-      <c r="M17" t="n">
-        <v>478.5122671977169</v>
-      </c>
-      <c r="N17" t="n">
-        <v>21.30430530091901</v>
-      </c>
-      <c r="O17" t="n">
-        <v>481.6841377562235</v>
-      </c>
-      <c r="P17" t="n">
-        <v>23.0206503480125</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>481.3399316591479</v>
-      </c>
       <c r="R17" t="n">
-        <v>22.87435531032768</v>
+        <v>474.85</v>
       </c>
       <c r="S17" t="n">
-        <v>483.6551569893954</v>
+        <v>19.83</v>
       </c>
       <c r="T17" t="n">
-        <v>24.95122339503231</v>
+        <v>475.64</v>
       </c>
       <c r="U17" t="n">
-        <v>482.9335037640204</v>
+        <v>19.18</v>
       </c>
       <c r="V17" t="n">
-        <v>23.72883687811895</v>
+        <v>478.51</v>
       </c>
       <c r="W17" t="n">
-        <v>483.7586793925616</v>
+        <v>21.3</v>
       </c>
       <c r="X17" t="n">
-        <v>22.54006257540036</v>
+        <v>481.68</v>
       </c>
       <c r="Y17" t="n">
-        <v>482.1853450762679</v>
+        <v>23.02</v>
       </c>
       <c r="Z17" t="n">
-        <v>21.84347049334095</v>
+        <v>481.34</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>22.87</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>483.66</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>24.95</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>482.93</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>23.73</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>483.76</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>22.54</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>482.19</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>21.84</v>
       </c>
       <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
         <v>491.025</v>
       </c>
-      <c r="AK17" t="n">
+      <c r="AT17" t="n">
         <v>488.0833333333333</v>
       </c>
-      <c r="AL17" t="n">
+      <c r="AU17" t="n">
         <v>486.5875</v>
       </c>
-      <c r="AM17" t="n">
+      <c r="AV17" t="n">
         <v>486.28</v>
       </c>
-      <c r="AN17" t="n">
+      <c r="AW17" t="n">
         <v>486.2083333333333</v>
       </c>
-      <c r="AO17" t="n">
+      <c r="AX17" t="n">
         <v>487.5071428571429</v>
       </c>
-      <c r="AP17" t="n">
+      <c r="AY17" t="n">
         <v>488.4375</v>
       </c>
-      <c r="AQ17" t="n">
+      <c r="AZ17" t="n">
         <v>488.4055555555556</v>
       </c>
-      <c r="AR17" t="n">
+      <c r="BA17" t="n">
         <v>488.56</v>
       </c>
-      <c r="AS17" t="n">
+      <c r="BB17" t="n">
         <v>69.13916672190952</v>
       </c>
-      <c r="AT17" t="n">
+      <c r="BC17" t="n">
         <v>58.85867018167804</v>
       </c>
-      <c r="AU17" t="n">
+      <c r="BD17" t="n">
         <v>52.53301194249193</v>
       </c>
-      <c r="AV17" t="n">
+      <c r="BE17" t="n">
         <v>48.74793944363187</v>
       </c>
-      <c r="AW17" t="n">
+      <c r="BF17" t="n">
         <v>46.05719195256649</v>
       </c>
-      <c r="AX17" t="n">
+      <c r="BG17" t="n">
         <v>44.01517537469669</v>
       </c>
-      <c r="AY17" t="n">
+      <c r="BH17" t="n">
         <v>42.54610550626226</v>
       </c>
-      <c r="AZ17" t="n">
+      <c r="BI17" t="n">
         <v>40.92455079808074</v>
       </c>
-      <c r="BA17" t="n">
+      <c r="BJ17" t="n">
         <v>39.56888171278031</v>
       </c>
-      <c r="BB17" t="n">
+      <c r="BK17" t="n">
         <v>338</v>
       </c>
-      <c r="BC17" t="n">
+      <c r="BL17" t="n">
         <v>338</v>
       </c>
-      <c r="BD17" t="n">
+      <c r="BM17" t="n">
         <v>338</v>
       </c>
-      <c r="BE17" t="n">
+      <c r="BN17" t="n">
         <v>338</v>
       </c>
-      <c r="BF17" t="n">
+      <c r="BO17" t="n">
         <v>338</v>
       </c>
-      <c r="BG17" t="n">
+      <c r="BP17" t="n">
         <v>338</v>
       </c>
-      <c r="BH17" t="n">
+      <c r="BQ17" t="n">
         <v>338</v>
       </c>
-      <c r="BI17" t="n">
+      <c r="BR17" t="n">
         <v>338</v>
       </c>
-      <c r="BJ17" t="n">
+      <c r="BS17" t="n">
         <v>338</v>
       </c>
-      <c r="BK17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>669</v>
-      </c>
       <c r="BT17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC17" t="n">
         <v>1</v>
       </c>
-      <c r="BU17" t="n">
+      <c r="CD17" t="n">
         <v>0.6111111111111112</v>
       </c>
-      <c r="BV17" t="n">
+      <c r="CE17" t="n">
         <v>0.6071428571428571</v>
       </c>
-      <c r="BW17" t="n">
+      <c r="CF17" t="n">
         <v>0.5789473684210527</v>
       </c>
-      <c r="BX17" t="n">
+      <c r="CG17" t="n">
         <v>0.5416666666666666</v>
       </c>
-      <c r="BY17" t="n">
+      <c r="CH17" t="n">
         <v>0.5961538461538461</v>
       </c>
-      <c r="BZ17" t="n">
+      <c r="CI17" t="n">
         <v>0.5818181818181818</v>
       </c>
-      <c r="CA17" t="n">
+      <c r="CJ17" t="n">
         <v>0.5538461538461539</v>
       </c>
-      <c r="CB17" t="n">
+      <c r="CK17" t="n">
         <v>0.5333333333333333</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>482.19</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>21.84</v>
       </c>
     </row>
     <row r="18">
@@ -4776,10 +5359,10 @@
         <v>478</v>
       </c>
       <c r="C18" t="n">
+        <v>32.61675315048184</v>
+      </c>
+      <c r="D18" t="n">
         <v>22</v>
-      </c>
-      <c r="D18" t="n">
-        <v>32.61675315048184</v>
       </c>
       <c r="E18" t="n">
         <v>478</v>
@@ -4788,228 +5371,261 @@
         <v>200</v>
       </c>
       <c r="G18" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="H18" t="inlineStr">
+        <v>80.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>473.9641819800204</v>
-      </c>
-      <c r="J18" t="n">
-        <v>26.12080659740202</v>
-      </c>
-      <c r="K18" t="n">
-        <v>471.2741599889564</v>
-      </c>
-      <c r="L18" t="n">
-        <v>26.74643056306405</v>
-      </c>
-      <c r="M18" t="n">
-        <v>472.8578137903614</v>
-      </c>
-      <c r="N18" t="n">
-        <v>32.18374920636239</v>
-      </c>
-      <c r="O18" t="n">
-        <v>473.880769488515</v>
-      </c>
-      <c r="P18" t="n">
-        <v>26.92489096580692</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>478.3428055637685</v>
-      </c>
       <c r="R18" t="n">
-        <v>27.70984691965701</v>
+        <v>473.96</v>
       </c>
       <c r="S18" t="n">
-        <v>478.7806848593833</v>
+        <v>26.12</v>
       </c>
       <c r="T18" t="n">
-        <v>25.6475044556452</v>
+        <v>471.27</v>
       </c>
       <c r="U18" t="n">
-        <v>481.6683865142257</v>
+        <v>26.75</v>
       </c>
       <c r="V18" t="n">
-        <v>25.63002670173842</v>
+        <v>472.86</v>
       </c>
       <c r="W18" t="n">
-        <v>482.1142287357965</v>
+        <v>32.18</v>
       </c>
       <c r="X18" t="n">
-        <v>25.32254878579646</v>
+        <v>473.88</v>
       </c>
       <c r="Y18" t="n">
-        <v>481.4220297853315</v>
+        <v>26.92</v>
       </c>
       <c r="Z18" t="n">
-        <v>25.8578296084116</v>
+        <v>478.34</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>27.71</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>478.78</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>25.65</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>481.67</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>25.63</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>482.11</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>25.32</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>481.42</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>25.86</v>
       </c>
       <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
         <v>484.95</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AT18" t="n">
         <v>484.0666666666667</v>
       </c>
-      <c r="AL18" t="n">
+      <c r="AU18" t="n">
         <v>481.925</v>
       </c>
-      <c r="AM18" t="n">
+      <c r="AV18" t="n">
         <v>480.98</v>
       </c>
-      <c r="AN18" t="n">
+      <c r="AW18" t="n">
         <v>480.9666666666666</v>
       </c>
-      <c r="AO18" t="n">
+      <c r="AX18" t="n">
         <v>481.5642857142857</v>
       </c>
-      <c r="AP18" t="n">
+      <c r="AY18" t="n">
         <v>483</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="AZ18" t="n">
         <v>483.5611111111111</v>
       </c>
-      <c r="AR18" t="n">
+      <c r="BA18" t="n">
         <v>483.87</v>
       </c>
-      <c r="AS18" t="n">
+      <c r="BB18" t="n">
         <v>72.09748608654812</v>
       </c>
-      <c r="AT18" t="n">
+      <c r="BC18" t="n">
         <v>62.00990960232799</v>
       </c>
-      <c r="AU18" t="n">
+      <c r="BD18" t="n">
         <v>56.74235080607782</v>
       </c>
-      <c r="AV18" t="n">
+      <c r="BE18" t="n">
         <v>53.19886840901787</v>
       </c>
-      <c r="AW18" t="n">
+      <c r="BF18" t="n">
         <v>50.1369679533531</v>
       </c>
-      <c r="AX18" t="n">
+      <c r="BG18" t="n">
         <v>47.28019982950968</v>
       </c>
-      <c r="AY18" t="n">
+      <c r="BH18" t="n">
         <v>44.71744625982124</v>
       </c>
-      <c r="AZ18" t="n">
+      <c r="BI18" t="n">
         <v>43.06379813574905</v>
       </c>
-      <c r="BA18" t="n">
+      <c r="BJ18" t="n">
         <v>41.98884494719996</v>
       </c>
-      <c r="BB18" t="n">
+      <c r="BK18" t="n">
         <v>343</v>
       </c>
-      <c r="BC18" t="n">
+      <c r="BL18" t="n">
         <v>343</v>
       </c>
-      <c r="BD18" t="n">
+      <c r="BM18" t="n">
         <v>343</v>
       </c>
-      <c r="BE18" t="n">
+      <c r="BN18" t="n">
         <v>343</v>
       </c>
-      <c r="BF18" t="n">
+      <c r="BO18" t="n">
         <v>343</v>
       </c>
-      <c r="BG18" t="n">
+      <c r="BP18" t="n">
         <v>343</v>
       </c>
-      <c r="BH18" t="n">
+      <c r="BQ18" t="n">
         <v>343</v>
       </c>
-      <c r="BI18" t="n">
+      <c r="BR18" t="n">
         <v>343</v>
       </c>
-      <c r="BJ18" t="n">
+      <c r="BS18" t="n">
         <v>343</v>
       </c>
-      <c r="BK18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>669</v>
-      </c>
       <c r="BT18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC18" t="n">
         <v>0.7</v>
       </c>
-      <c r="BU18" t="n">
+      <c r="CD18" t="n">
         <v>0.7894736842105263</v>
       </c>
-      <c r="BV18" t="n">
+      <c r="CE18" t="n">
         <v>0.7241379310344828</v>
       </c>
-      <c r="BW18" t="n">
+      <c r="CF18" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BX18" t="n">
+      <c r="CG18" t="n">
         <v>0.6530612244897959</v>
       </c>
-      <c r="BY18" t="n">
+      <c r="CH18" t="n">
         <v>0.5964912280701754</v>
       </c>
-      <c r="BZ18" t="n">
+      <c r="CI18" t="n">
         <v>0.5666666666666667</v>
       </c>
-      <c r="CA18" t="n">
+      <c r="CJ18" t="n">
         <v>0.5151515151515151</v>
       </c>
-      <c r="CB18" t="n">
+      <c r="CK18" t="n">
         <v>0.472972972972973</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>481.42</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>25.86</v>
       </c>
     </row>
     <row r="19">
@@ -5022,10 +5638,10 @@
         <v>482</v>
       </c>
       <c r="C19" t="n">
+        <v>32.61675315048184</v>
+      </c>
+      <c r="D19" t="n">
         <v>22</v>
-      </c>
-      <c r="D19" t="n">
-        <v>32.61675315048184</v>
       </c>
       <c r="E19" t="n">
         <v>482</v>
@@ -5034,720 +5650,819 @@
         <v>200</v>
       </c>
       <c r="G19" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="H19" t="inlineStr">
+        <v>81.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>496.7657939764282</v>
-      </c>
-      <c r="J19" t="n">
-        <v>20.68331214927859</v>
-      </c>
-      <c r="K19" t="n">
-        <v>485.4264319402334</v>
-      </c>
-      <c r="L19" t="n">
-        <v>26.98580819815613</v>
-      </c>
-      <c r="M19" t="n">
-        <v>482.7446788084704</v>
-      </c>
-      <c r="N19" t="n">
-        <v>26.45521135886218</v>
-      </c>
-      <c r="O19" t="n">
-        <v>480.8789795859333</v>
-      </c>
-      <c r="P19" t="n">
-        <v>25.7307748464035</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>482.9360821282397</v>
-      </c>
       <c r="R19" t="n">
-        <v>26.96375986918021</v>
+        <v>496.77</v>
       </c>
       <c r="S19" t="n">
-        <v>480.0643997157704</v>
+        <v>20.68</v>
       </c>
       <c r="T19" t="n">
-        <v>29.28795950052885</v>
+        <v>485.43</v>
       </c>
       <c r="U19" t="n">
-        <v>478.8700642571156</v>
+        <v>26.99</v>
       </c>
       <c r="V19" t="n">
-        <v>30.17476582316902</v>
+        <v>482.74</v>
       </c>
       <c r="W19" t="n">
-        <v>477.4021355356298</v>
+        <v>26.46</v>
       </c>
       <c r="X19" t="n">
-        <v>28.68671428194697</v>
+        <v>480.88</v>
       </c>
       <c r="Y19" t="n">
-        <v>479.3567144905621</v>
+        <v>25.73</v>
       </c>
       <c r="Z19" t="n">
-        <v>28.26767768227625</v>
+        <v>482.94</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>26.96</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>480.06</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>29.29</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>478.87</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>30.17</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>477.4</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>28.69</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>479.36</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>28.27</v>
       </c>
       <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
         <v>494.3</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AT19" t="n">
         <v>491.9166666666667</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AU19" t="n">
         <v>489.5625</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="AV19" t="n">
         <v>487.65</v>
       </c>
-      <c r="AN19" t="n">
+      <c r="AW19" t="n">
         <v>487.1666666666667</v>
       </c>
-      <c r="AO19" t="n">
+      <c r="AX19" t="n">
         <v>485.9571428571429</v>
       </c>
-      <c r="AP19" t="n">
+      <c r="AY19" t="n">
         <v>484.9</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AZ19" t="n">
         <v>483.3722222222222</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="BA19" t="n">
         <v>482.76</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="BB19" t="n">
         <v>67.50785139522661</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="BC19" t="n">
         <v>58.93054999083432</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="BD19" t="n">
         <v>53.74659146169178</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="BE19" t="n">
         <v>50.63326475746948</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="BF19" t="n">
         <v>48.11450462756065</v>
       </c>
-      <c r="AX19" t="n">
+      <c r="BG19" t="n">
         <v>46.33956523449965</v>
       </c>
-      <c r="AY19" t="n">
+      <c r="BH19" t="n">
         <v>45.25030386638304</v>
       </c>
-      <c r="AZ19" t="n">
+      <c r="BI19" t="n">
         <v>44.97369979042758</v>
       </c>
-      <c r="BA19" t="n">
+      <c r="BJ19" t="n">
         <v>44.44876151255511</v>
       </c>
-      <c r="BB19" t="n">
+      <c r="BK19" t="n">
         <v>328</v>
       </c>
-      <c r="BC19" t="n">
+      <c r="BL19" t="n">
         <v>328</v>
       </c>
-      <c r="BD19" t="n">
+      <c r="BM19" t="n">
         <v>328</v>
       </c>
-      <c r="BE19" t="n">
+      <c r="BN19" t="n">
         <v>328</v>
       </c>
-      <c r="BF19" t="n">
+      <c r="BO19" t="n">
         <v>328</v>
       </c>
-      <c r="BG19" t="n">
+      <c r="BP19" t="n">
         <v>328</v>
       </c>
-      <c r="BH19" t="n">
+      <c r="BQ19" t="n">
         <v>328</v>
       </c>
-      <c r="BI19" t="n">
+      <c r="BR19" t="n">
         <v>328</v>
       </c>
-      <c r="BJ19" t="n">
+      <c r="BS19" t="n">
         <v>328</v>
       </c>
-      <c r="BK19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>669</v>
-      </c>
       <c r="BT19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC19" t="n">
         <v>1</v>
       </c>
-      <c r="BU19" t="n">
+      <c r="CD19" t="n">
         <v>0.5294117647058824</v>
       </c>
-      <c r="BV19" t="n">
+      <c r="CE19" t="n">
         <v>0.5909090909090909</v>
       </c>
-      <c r="BW19" t="n">
+      <c r="CF19" t="n">
         <v>0.75</v>
       </c>
-      <c r="BX19" t="n">
+      <c r="CG19" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BY19" t="n">
+      <c r="CH19" t="n">
         <v>0.9090909090909091</v>
       </c>
-      <c r="BZ19" t="n">
+      <c r="CI19" t="n">
         <v>0.875</v>
       </c>
-      <c r="CA19" t="n">
+      <c r="CJ19" t="n">
         <v>0.7659574468085106</v>
       </c>
-      <c r="CB19" t="n">
+      <c r="CK19" t="n">
         <v>0.7169811320754716</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>479.36</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>28.27</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S20_G1_481_20_REL2</t>
+          <t>S19_G1_479_18_REL2</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C20" t="n">
-        <v>20</v>
+        <v>26.68643439584878</v>
       </c>
       <c r="D20" t="n">
-        <v>29.65159377316531</v>
+        <v>18</v>
       </c>
       <c r="E20" t="n">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="F20" t="n">
         <v>200</v>
       </c>
       <c r="G20" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="H20" t="inlineStr">
+        <v>83</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>488.4071034091788</v>
-      </c>
-      <c r="J20" t="n">
-        <v>25.25043059542425</v>
-      </c>
-      <c r="K20" t="n">
-        <v>481.3204969211408</v>
-      </c>
-      <c r="L20" t="n">
-        <v>27.83340978012532</v>
-      </c>
-      <c r="M20" t="n">
-        <v>489.9148805042992</v>
-      </c>
-      <c r="N20" t="n">
-        <v>31.48765515225026</v>
-      </c>
-      <c r="O20" t="n">
-        <v>487.9518308315924</v>
-      </c>
-      <c r="P20" t="n">
-        <v>29.53954267133113</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>486.7029695103295</v>
-      </c>
       <c r="R20" t="n">
-        <v>30.69083116450001</v>
+        <v>490.55</v>
       </c>
       <c r="S20" t="n">
-        <v>481.2054132592883</v>
+        <v>26.68</v>
       </c>
       <c r="T20" t="n">
-        <v>31.0347297620039</v>
+        <v>481.2</v>
       </c>
       <c r="U20" t="n">
-        <v>479.5583280693243</v>
+        <v>29.42</v>
       </c>
       <c r="V20" t="n">
-        <v>29.29411492152204</v>
+        <v>474.87</v>
       </c>
       <c r="W20" t="n">
-        <v>478.9582106841479</v>
+        <v>27.81</v>
       </c>
       <c r="X20" t="n">
-        <v>27.37031719670322</v>
+        <v>475.1</v>
       </c>
       <c r="Y20" t="n">
-        <v>478.6687816770968</v>
+        <v>25.91</v>
       </c>
       <c r="Z20" t="n">
-        <v>26.79165681149509</v>
+        <v>478.41</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>28.21</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>481.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>28.49</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>480.44</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>27.64</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>480.79</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>480.39</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>24.94</v>
       </c>
       <c r="AJ20" t="n">
-        <v>494.825</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>491.8333333333333</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>490.6625</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>490</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>489.7083333333333</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>488.5428571428571</v>
+        <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>486.95625</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>487.0833333333333</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>486.825</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>70.27869076042894</v>
+        <v>498.95</v>
       </c>
       <c r="AT20" t="n">
-        <v>60.94647013750856</v>
+        <v>492.8666666666667</v>
       </c>
       <c r="AU20" t="n">
-        <v>55.9238195561605</v>
+        <v>487.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>52.51304599811365</v>
+        <v>485.21</v>
       </c>
       <c r="AW20" t="n">
-        <v>50.21228200240344</v>
+        <v>483.8083333333333</v>
       </c>
       <c r="AX20" t="n">
-        <v>48.73959543600363</v>
+        <v>485.1928571428571</v>
       </c>
       <c r="AY20" t="n">
-        <v>48.51267191092963</v>
+        <v>485.28125</v>
       </c>
       <c r="AZ20" t="n">
-        <v>47.01558547734759</v>
+        <v>485.4277777777778</v>
       </c>
       <c r="BA20" t="n">
-        <v>46.07650567263104</v>
+        <v>485.845</v>
       </c>
       <c r="BB20" t="n">
-        <v>323</v>
+        <v>67.79710539543706</v>
       </c>
       <c r="BC20" t="n">
-        <v>323</v>
+        <v>59.95205491798333</v>
       </c>
       <c r="BD20" t="n">
-        <v>323</v>
+        <v>56.14788508928898</v>
       </c>
       <c r="BE20" t="n">
-        <v>323</v>
+        <v>52.38325973056659</v>
       </c>
       <c r="BF20" t="n">
-        <v>323</v>
+        <v>50.0523552281897</v>
       </c>
       <c r="BG20" t="n">
-        <v>323</v>
+        <v>48.28367018073967</v>
       </c>
       <c r="BH20" t="n">
-        <v>323</v>
+        <v>47.11583755423965</v>
       </c>
       <c r="BI20" t="n">
-        <v>323</v>
+        <v>45.7382687516161</v>
       </c>
       <c r="BJ20" t="n">
-        <v>323</v>
+        <v>44.28973893578512</v>
       </c>
       <c r="BK20" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BL20" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BM20" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BN20" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BO20" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BP20" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BQ20" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BR20" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BS20" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BT20" t="n">
-        <v>0.8888888888888888</v>
+        <v>669</v>
       </c>
       <c r="BU20" t="n">
-        <v>0.7894736842105263</v>
+        <v>669</v>
       </c>
       <c r="BV20" t="n">
-        <v>0.6896551724137931</v>
+        <v>669</v>
       </c>
       <c r="BW20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC20" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="CD20" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CE20" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="CF20" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="CG20" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="CH20" t="n">
+        <v>0.05405405405405406</v>
+      </c>
+      <c r="CI20" t="n">
         <v>0.6153846153846154</v>
       </c>
-      <c r="BX20" t="n">
-        <v>0.6122448979591837</v>
-      </c>
-      <c r="BY20" t="n">
-        <v>0.6226415094339622</v>
-      </c>
-      <c r="BZ20" t="n">
-        <v>0.6415094339622641</v>
-      </c>
-      <c r="CA20" t="n">
-        <v>0.7358490566037735</v>
-      </c>
-      <c r="CB20" t="n">
-        <v>0.8363636363636363</v>
+      <c r="CJ20" t="n">
+        <v>0.6818181818181818</v>
+      </c>
+      <c r="CK20" t="n">
+        <v>0.5740740740740741</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>480.39</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>24.94</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S19_G1_479_18_REL2</t>
+          <t>S20_G1_481_20_REL2</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C21" t="n">
-        <v>18</v>
+        <v>29.65159377316531</v>
       </c>
       <c r="D21" t="n">
-        <v>26.68643439584878</v>
+        <v>20</v>
       </c>
       <c r="E21" t="n">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="F21" t="n">
         <v>200</v>
       </c>
       <c r="G21" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="H21" t="inlineStr">
+        <v>84</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>490.5510348118721</v>
-      </c>
-      <c r="J21" t="n">
-        <v>26.68412318274572</v>
-      </c>
-      <c r="K21" t="n">
-        <v>481.2015120898386</v>
-      </c>
-      <c r="L21" t="n">
-        <v>29.41939938355011</v>
-      </c>
-      <c r="M21" t="n">
-        <v>474.8694308675986</v>
-      </c>
-      <c r="N21" t="n">
-        <v>27.81064337088678</v>
-      </c>
-      <c r="O21" t="n">
-        <v>475.0958600425255</v>
-      </c>
-      <c r="P21" t="n">
-        <v>25.91383571996667</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>478.4096310348925</v>
-      </c>
       <c r="R21" t="n">
-        <v>28.21238281082601</v>
+        <v>488.41</v>
       </c>
       <c r="S21" t="n">
-        <v>481.1015636203992</v>
+        <v>25.25</v>
       </c>
       <c r="T21" t="n">
-        <v>28.48996627266083</v>
+        <v>481.32</v>
       </c>
       <c r="U21" t="n">
-        <v>480.4353802316347</v>
+        <v>27.83</v>
       </c>
       <c r="V21" t="n">
-        <v>27.63511224627936</v>
+        <v>489.91</v>
       </c>
       <c r="W21" t="n">
-        <v>480.7853644307301</v>
+        <v>31.49</v>
       </c>
       <c r="X21" t="n">
-        <v>26.00062348371222</v>
+        <v>487.95</v>
       </c>
       <c r="Y21" t="n">
-        <v>480.3907694968117</v>
+        <v>29.54</v>
       </c>
       <c r="Z21" t="n">
-        <v>24.93642296861394</v>
+        <v>486.7</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>30.69</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>481.21</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>31.03</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>479.56</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>29.29</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>478.96</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>27.37</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>478.67</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>26.79</v>
       </c>
       <c r="AJ21" t="n">
-        <v>498.95</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>492.8666666666667</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>487.8</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>485.21</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>483.8083333333333</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>485.1928571428571</v>
+        <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>485.28125</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>485.4277777777778</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>485.845</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>67.79710539543706</v>
+        <v>494.825</v>
       </c>
       <c r="AT21" t="n">
-        <v>59.95205491798333</v>
+        <v>491.8333333333333</v>
       </c>
       <c r="AU21" t="n">
-        <v>56.14788508928898</v>
+        <v>490.6625</v>
       </c>
       <c r="AV21" t="n">
-        <v>52.38325973056659</v>
+        <v>490</v>
       </c>
       <c r="AW21" t="n">
-        <v>50.0523552281897</v>
+        <v>489.7083333333333</v>
       </c>
       <c r="AX21" t="n">
-        <v>48.28367018073967</v>
+        <v>488.5428571428571</v>
       </c>
       <c r="AY21" t="n">
-        <v>47.11583755423965</v>
+        <v>486.95625</v>
       </c>
       <c r="AZ21" t="n">
-        <v>45.7382687516161</v>
+        <v>487.0833333333333</v>
       </c>
       <c r="BA21" t="n">
-        <v>44.28973893578512</v>
+        <v>486.825</v>
       </c>
       <c r="BB21" t="n">
-        <v>330</v>
+        <v>70.27869076042894</v>
       </c>
       <c r="BC21" t="n">
-        <v>330</v>
+        <v>60.94647013750856</v>
       </c>
       <c r="BD21" t="n">
-        <v>330</v>
+        <v>55.9238195561605</v>
       </c>
       <c r="BE21" t="n">
-        <v>330</v>
+        <v>52.51304599811365</v>
       </c>
       <c r="BF21" t="n">
-        <v>330</v>
+        <v>50.21228200240344</v>
       </c>
       <c r="BG21" t="n">
-        <v>330</v>
+        <v>48.73959543600363</v>
       </c>
       <c r="BH21" t="n">
-        <v>330</v>
+        <v>48.51267191092963</v>
       </c>
       <c r="BI21" t="n">
-        <v>330</v>
+        <v>47.01558547734759</v>
       </c>
       <c r="BJ21" t="n">
-        <v>330</v>
+        <v>46.07650567263104</v>
       </c>
       <c r="BK21" t="n">
-        <v>669</v>
+        <v>323</v>
       </c>
       <c r="BL21" t="n">
-        <v>669</v>
+        <v>323</v>
       </c>
       <c r="BM21" t="n">
-        <v>669</v>
+        <v>323</v>
       </c>
       <c r="BN21" t="n">
-        <v>669</v>
+        <v>323</v>
       </c>
       <c r="BO21" t="n">
-        <v>669</v>
+        <v>323</v>
       </c>
       <c r="BP21" t="n">
-        <v>669</v>
+        <v>323</v>
       </c>
       <c r="BQ21" t="n">
-        <v>669</v>
+        <v>323</v>
       </c>
       <c r="BR21" t="n">
-        <v>669</v>
+        <v>323</v>
       </c>
       <c r="BS21" t="n">
-        <v>669</v>
+        <v>323</v>
       </c>
       <c r="BT21" t="n">
-        <v>0.5833333333333334</v>
+        <v>669</v>
       </c>
       <c r="BU21" t="n">
-        <v>0.75</v>
+        <v>669</v>
       </c>
       <c r="BV21" t="n">
-        <v>0.1666666666666667</v>
+        <v>669</v>
       </c>
       <c r="BW21" t="n">
-        <v>0.6923076923076923</v>
+        <v>669</v>
       </c>
       <c r="BX21" t="n">
-        <v>0.5833333333333334</v>
+        <v>669</v>
       </c>
       <c r="BY21" t="n">
-        <v>0.05405405405405406</v>
+        <v>669</v>
       </c>
       <c r="BZ21" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB21" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC21" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="CD21" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="CE21" t="n">
+        <v>0.6896551724137931</v>
+      </c>
+      <c r="CF21" t="n">
         <v>0.6153846153846154</v>
       </c>
-      <c r="CA21" t="n">
-        <v>0.6818181818181818</v>
-      </c>
-      <c r="CB21" t="n">
-        <v>0.5740740740740741</v>
+      <c r="CG21" t="n">
+        <v>0.6122448979591837</v>
+      </c>
+      <c r="CH21" t="n">
+        <v>0.6226415094339622</v>
+      </c>
+      <c r="CI21" t="n">
+        <v>0.6415094339622641</v>
+      </c>
+      <c r="CJ21" t="n">
+        <v>0.7358490566037735</v>
+      </c>
+      <c r="CK21" t="n">
+        <v>0.8363636363636363</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>478.67</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>26.79</v>
       </c>
     </row>
     <row r="22">
@@ -5760,10 +6475,10 @@
         <v>479.65</v>
       </c>
       <c r="C22" t="n">
+        <v>29.42920681986657</v>
+      </c>
+      <c r="D22" t="n">
         <v>19.85</v>
-      </c>
-      <c r="D22" t="n">
-        <v>29.42920681986657</v>
       </c>
       <c r="E22" t="n">
         <v>479.65</v>
@@ -5772,224 +6487,239 @@
         <v>200</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5447500000000002</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>82.875</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.22</v>
+      </c>
       <c r="I22" t="n">
-        <v>476.9562114200642</v>
+        <v>2.117</v>
       </c>
       <c r="J22" t="n">
-        <v>23.50700242218804</v>
+        <v>2.0915</v>
       </c>
       <c r="K22" t="n">
-        <v>477.6895613413364</v>
+        <v>2.069</v>
       </c>
       <c r="L22" t="n">
-        <v>24.44087866347175</v>
+        <v>2.0445</v>
       </c>
       <c r="M22" t="n">
-        <v>477.7047523248815</v>
+        <v>2.031499999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>24.60949826006975</v>
+        <v>2.7515</v>
       </c>
       <c r="O22" t="n">
-        <v>478.5334137705628</v>
+        <v>2.502</v>
       </c>
       <c r="P22" t="n">
-        <v>24.25946163018869</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>478.2069130590857</v>
-      </c>
+        <v>2.337</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>24.31299090729107</v>
+        <v>476.956</v>
       </c>
       <c r="S22" t="n">
-        <v>478.3217541734069</v>
+        <v>23.5075</v>
       </c>
       <c r="T22" t="n">
-        <v>24.51727175963786</v>
+        <v>477.6900000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>478.0727881081122</v>
+        <v>24.4415</v>
       </c>
       <c r="V22" t="n">
-        <v>24.37291763492319</v>
+        <v>477.7045</v>
       </c>
       <c r="W22" t="n">
-        <v>478.2148654522944</v>
+        <v>24.6095</v>
       </c>
       <c r="X22" t="n">
-        <v>23.75860221896842</v>
+        <v>478.5335000000001</v>
       </c>
       <c r="Y22" t="n">
-        <v>478.0645169145117</v>
+        <v>24.25850000000001</v>
       </c>
       <c r="Z22" t="n">
-        <v>23.59413258415834</v>
+        <v>478.206</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>24.3125</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>478.3219999999999</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>24.516</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>478.0735000000001</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>24.372</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>478.216</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>23.759</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>478.0649999999999</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>23.5945</v>
       </c>
       <c r="AJ22" t="n">
-        <v>489.4562500000001</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>486.8958333333334</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>485.6156249999999</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>489.4555</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>486.8950000000001</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>485.6155</v>
+      </c>
+      <c r="AV22" t="n">
         <v>484.6985</v>
       </c>
-      <c r="AN22" t="n">
+      <c r="AW22" t="n">
         <v>484.2474999999999</v>
       </c>
-      <c r="AO22" t="n">
-        <v>484.1125</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>484.0124999999999</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>483.9447222222222</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>483.922</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>71.53580252092453</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>61.59040214969373</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>55.56143245242517</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>51.50715184435914</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>48.59735573598099</v>
-      </c>
       <c r="AX22" t="n">
-        <v>46.31350786130686</v>
+        <v>484.113</v>
       </c>
       <c r="AY22" t="n">
-        <v>44.63713442893801</v>
+        <v>484.0125</v>
       </c>
       <c r="AZ22" t="n">
-        <v>43.21116518382775</v>
+        <v>483.9445000000001</v>
       </c>
       <c r="BA22" t="n">
-        <v>41.97652232131914</v>
+        <v>483.9215</v>
       </c>
       <c r="BB22" t="n">
+        <v>71.53649999999999</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>61.59000000000001</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>55.56100000000001</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>51.5065</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>48.59699999999999</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>46.314</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>44.638</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>43.211</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>41.9765</v>
+      </c>
+      <c r="BK22" t="n">
         <v>331.25</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BL22" t="n">
         <v>331.25</v>
       </c>
-      <c r="BD22" t="n">
+      <c r="BM22" t="n">
         <v>331.25</v>
       </c>
-      <c r="BE22" t="n">
+      <c r="BN22" t="n">
         <v>331.25</v>
       </c>
-      <c r="BF22" t="n">
+      <c r="BO22" t="n">
         <v>331.25</v>
       </c>
-      <c r="BG22" t="n">
+      <c r="BP22" t="n">
         <v>331.25</v>
       </c>
-      <c r="BH22" t="n">
+      <c r="BQ22" t="n">
         <v>331.25</v>
       </c>
-      <c r="BI22" t="n">
+      <c r="BR22" t="n">
         <v>331.25</v>
       </c>
-      <c r="BJ22" t="n">
+      <c r="BS22" t="n">
         <v>331.25</v>
       </c>
-      <c r="BK22" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM22" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN22" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO22" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP22" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ22" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR22" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS22" t="n">
-        <v>669</v>
-      </c>
       <c r="BT22" t="n">
-        <v>0.7297709235209235</v>
+        <v>669</v>
       </c>
       <c r="BU22" t="n">
-        <v>0.6554913043612733</v>
+        <v>669</v>
       </c>
       <c r="BV22" t="n">
-        <v>0.5655662682890126</v>
+        <v>669</v>
       </c>
       <c r="BW22" t="n">
-        <v>0.6457000827853822</v>
+        <v>669</v>
       </c>
       <c r="BX22" t="n">
-        <v>0.6371639612129365</v>
+        <v>669</v>
       </c>
       <c r="BY22" t="n">
-        <v>0.6045605449264781</v>
+        <v>669</v>
       </c>
       <c r="BZ22" t="n">
-        <v>0.6108970298739611</v>
+        <v>669</v>
       </c>
       <c r="CA22" t="n">
-        <v>0.6610715381766863</v>
+        <v>669</v>
       </c>
       <c r="CB22" t="n">
-        <v>0.67401084560923</v>
+        <v>669</v>
+      </c>
+      <c r="CC22" t="inlineStr"/>
+      <c r="CD22" t="inlineStr"/>
+      <c r="CE22" t="inlineStr"/>
+      <c r="CF22" t="inlineStr"/>
+      <c r="CG22" t="inlineStr"/>
+      <c r="CH22" t="inlineStr"/>
+      <c r="CI22" t="inlineStr"/>
+      <c r="CJ22" t="inlineStr"/>
+      <c r="CK22" t="inlineStr"/>
+      <c r="CL22" t="n">
+        <v>478.0649999999999</v>
+      </c>
+      <c r="CM22" t="n">
+        <v>23.5945</v>
       </c>
     </row>
     <row r="23">
@@ -6002,10 +6732,10 @@
         <v>1.424411235711461</v>
       </c>
       <c r="C23" t="n">
+        <v>2.369931877634437</v>
+      </c>
+      <c r="D23" t="n">
         <v>1.598519051464429</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2.369931877634437</v>
       </c>
       <c r="E23" t="n">
         <v>1.424411235711461</v>
@@ -6014,224 +6744,239 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01874166481399131</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>1.190698600778021</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.118721256909221</v>
+      </c>
       <c r="I23" t="n">
-        <v>12.10596563772976</v>
+        <v>0.1224787844141954</v>
       </c>
       <c r="J23" t="n">
-        <v>6.087142409339439</v>
+        <v>0.1176647780773839</v>
       </c>
       <c r="K23" t="n">
-        <v>7.817865631796867</v>
+        <v>0.1266532772239983</v>
       </c>
       <c r="L23" t="n">
-        <v>4.153004755009182</v>
+        <v>0.1285332232291878</v>
       </c>
       <c r="M23" t="n">
-        <v>6.041818161732755</v>
+        <v>0.1153609894840402</v>
       </c>
       <c r="N23" t="n">
-        <v>4.403080322648889</v>
+        <v>0.1216238809652637</v>
       </c>
       <c r="O23" t="n">
-        <v>4.912496813873691</v>
+        <v>0.08439256639750858</v>
       </c>
       <c r="P23" t="n">
-        <v>3.565857815484222</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>5.319435780987829</v>
-      </c>
+        <v>0.08862101449727547</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>4.069593498387448</v>
+        <v>12.10660819987428</v>
       </c>
       <c r="S23" t="n">
-        <v>5.5484943310088</v>
+        <v>6.086230252316332</v>
       </c>
       <c r="T23" t="n">
-        <v>3.864514967481764</v>
+        <v>7.817437324071717</v>
       </c>
       <c r="U23" t="n">
-        <v>4.957504963957282</v>
+        <v>4.153968647729035</v>
       </c>
       <c r="V23" t="n">
-        <v>3.424034903884317</v>
+        <v>6.040915297500781</v>
       </c>
       <c r="W23" t="n">
-        <v>4.635319154632164</v>
+        <v>4.403072461959166</v>
       </c>
       <c r="X23" t="n">
-        <v>3.373453193863502</v>
+        <v>4.911759546446187</v>
       </c>
       <c r="Y23" t="n">
-        <v>3.903745492743498</v>
+        <v>3.566111364379679</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.210400035017898</v>
+        <v>5.319828252075339</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>4.070005657567515</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>5.549488928579008</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.865718970372101</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>4.957297942905678</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>3.424055152039834</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>4.635183979769927</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>3.373016610192066</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>3.903638653467053</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>3.210075380324957</v>
       </c>
       <c r="AJ23" t="n">
-        <v>5.370116355448231</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>4.823513542505815</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>4.235130479798833</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>5.368678632881454</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>4.824031399915265</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>4.234847260030698</v>
+      </c>
+      <c r="AV23" t="n">
         <v>3.923660046167962</v>
       </c>
-      <c r="AN23" t="n">
-        <v>3.735672532356901</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>3.52820070120308</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>3.530196920293912</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>3.341974897433362</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>3.126326413237317</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>3.200049578117302</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>2.964889914448594</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>2.748318341726321</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>2.682997907316505</v>
-      </c>
       <c r="AW23" t="n">
-        <v>2.680653052462704</v>
+        <v>3.735816510483348</v>
       </c>
       <c r="AX23" t="n">
-        <v>2.702026587378086</v>
+        <v>3.528424577626683</v>
       </c>
       <c r="AY23" t="n">
-        <v>2.875490428040979</v>
+        <v>3.530914411161413</v>
       </c>
       <c r="AZ23" t="n">
-        <v>2.939320500110104</v>
+        <v>3.343390140497954</v>
       </c>
       <c r="BA23" t="n">
-        <v>2.889958806443871</v>
+        <v>3.127822977559216</v>
       </c>
       <c r="BB23" t="n">
+        <v>3.199067750718044</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>2.964898152151534</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>2.747597802483202</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>2.683123229215889</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>2.681617932674621</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>2.701536404968185</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>2.874850293585096</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>2.939253217006696</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>2.890338306550947</v>
+      </c>
+      <c r="BK23" t="n">
         <v>8.842927593339924</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BL23" t="n">
         <v>8.842927593339924</v>
       </c>
-      <c r="BD23" t="n">
+      <c r="BM23" t="n">
         <v>8.842927593339924</v>
       </c>
-      <c r="BE23" t="n">
+      <c r="BN23" t="n">
         <v>8.842927593339924</v>
       </c>
-      <c r="BF23" t="n">
+      <c r="BO23" t="n">
         <v>8.842927593339924</v>
       </c>
-      <c r="BG23" t="n">
+      <c r="BP23" t="n">
         <v>8.842927593339924</v>
       </c>
-      <c r="BH23" t="n">
+      <c r="BQ23" t="n">
         <v>8.842927593339924</v>
       </c>
-      <c r="BI23" t="n">
+      <c r="BR23" t="n">
         <v>8.842927593339924</v>
       </c>
-      <c r="BJ23" t="n">
+      <c r="BS23" t="n">
         <v>8.842927593339924</v>
       </c>
-      <c r="BK23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS23" t="n">
-        <v>0</v>
-      </c>
       <c r="BT23" t="n">
-        <v>0.2973503561166772</v>
+        <v>0</v>
       </c>
       <c r="BU23" t="n">
-        <v>0.2104145230170892</v>
+        <v>0</v>
       </c>
       <c r="BV23" t="n">
-        <v>0.2623236983413046</v>
+        <v>0</v>
       </c>
       <c r="BW23" t="n">
-        <v>0.2103007934161434</v>
+        <v>0</v>
       </c>
       <c r="BX23" t="n">
-        <v>0.2119631004835354</v>
+        <v>0</v>
       </c>
       <c r="BY23" t="n">
-        <v>0.2901023204287799</v>
+        <v>0</v>
       </c>
       <c r="BZ23" t="n">
-        <v>0.2459407550329649</v>
+        <v>0</v>
       </c>
       <c r="CA23" t="n">
-        <v>0.2227762000055012</v>
+        <v>0</v>
       </c>
       <c r="CB23" t="n">
-        <v>0.161398355546663</v>
+        <v>0</v>
+      </c>
+      <c r="CC23" t="inlineStr"/>
+      <c r="CD23" t="inlineStr"/>
+      <c r="CE23" t="inlineStr"/>
+      <c r="CF23" t="inlineStr"/>
+      <c r="CG23" t="inlineStr"/>
+      <c r="CH23" t="inlineStr"/>
+      <c r="CI23" t="inlineStr"/>
+      <c r="CJ23" t="inlineStr"/>
+      <c r="CK23" t="inlineStr"/>
+      <c r="CL23" t="n">
+        <v>3.903638653467053</v>
+      </c>
+      <c r="CM23" t="n">
+        <v>3.210075380324957</v>
       </c>
     </row>
   </sheetData>
